--- a/posicoes/BTG.xlsx
+++ b/posicoes/BTG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Reeadca9d276b44f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rb92e7df9aea64029"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -237,7 +237,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23086836</x:v>
+        <x:v>13433052</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -293,16 +293,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c>
-        <x:v>178766.26</x:v>
-      </x:c>
-      <x:c>
-        <x:v>6784.09</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>171982.17</x:v>
+        <x:v>178854.74</x:v>
+      </x:c>
+      <x:c>
+        <x:v>6799.58</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>172055.16</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -324,7 +324,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24121267</x:v>
+        <x:v>11539151</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -411,7 +411,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25758043</x:v>
+        <x:v>11706912</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -467,16 +467,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c>
-        <x:v>90760.22</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>90760.22</x:v>
+        <x:v>90800.63</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>90800.63</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -498,7 +498,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27732739</x:v>
+        <x:v>3601163</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -585,7 +585,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27361449</x:v>
+        <x:v>10094046</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -672,7 +672,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1545732</x:v>
+        <x:v>5703195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +759,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17382177</x:v>
+        <x:v>5244924</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -846,7 +846,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23560027</x:v>
+        <x:v>13878280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -933,7 +933,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22432648</x:v>
+        <x:v>13980808</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1020,7 +1020,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1680995</x:v>
+        <x:v>6542240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1107,7 +1107,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28535816</x:v>
+        <x:v>8961517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1194,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1318704</x:v>
+        <x:v>5751792</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1281,7 +1281,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21247964</x:v>
+        <x:v>317116</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1368,7 +1368,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23384490</x:v>
+        <x:v>13010668</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1455,7 +1455,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29028127</x:v>
+        <x:v>7556291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1542,7 +1542,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26812643</x:v>
+        <x:v>9603393</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +1629,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22036664</x:v>
+        <x:v>614762</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1716,7 +1716,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24729467</x:v>
+        <x:v>12588916</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1803,7 +1803,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20550434</x:v>
+        <x:v>1013236</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1890,7 +1890,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25673802</x:v>
+        <x:v>11666171</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1934,14 +1934,14 @@
         <x:v>1155</x:v>
       </x:c>
       <x:c>
-        <x:v>119992.95</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>119992.95</x:v>
+        <x:v>120004.5</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>120004.5</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -1963,7 +1963,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22327603</x:v>
+        <x:v>2179615</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2007,14 +2007,14 @@
         <x:v>694</x:v>
       </x:c>
       <x:c>
-        <x:v>71690.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>71690.2</x:v>
+        <x:v>71933.1</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>71933.1</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2036,7 +2036,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19444543</x:v>
+        <x:v>14102942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2080,14 +2080,14 @@
         <x:v>417</x:v>
       </x:c>
       <x:c>
-        <x:v>42825.9</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>42825.9</x:v>
+        <x:v>42846.75</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>42846.75</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2109,7 +2109,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24432184</x:v>
+        <x:v>13458462</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2182,7 +2182,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8350276</x:v>
+        <x:v>5004300</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2257,7 +2257,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2552390</x:v>
+        <x:v>6173566</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2332,7 +2332,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1343165</x:v>
+        <x:v>5847427</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2407,7 +2407,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18001803</x:v>
+        <x:v>4505669</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2451,16 +2451,16 @@
         <x:v>86.7568983</x:v>
       </x:c>
       <x:c>
-        <x:v>26367.19</x:v>
-      </x:c>
-      <x:c>
-        <x:v>82.62</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>26284.57</x:v>
+        <x:v>26380.08</x:v>
+      </x:c>
+      <x:c>
+        <x:v>85.52</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>26294.56</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2482,7 +2482,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18928252</x:v>
+        <x:v>3584547</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2557,7 +2557,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18377897</x:v>
+        <x:v>3202744</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2632,7 +2632,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28698901</x:v>
+        <x:v>7876742</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2707,7 +2707,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20146462</x:v>
+        <x:v>2471935</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2751,16 +2751,16 @@
         <x:v>29040.5557123</x:v>
       </x:c>
       <x:c>
-        <x:v>30133.11</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>30133.11</x:v>
+        <x:v>30065.75</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>30065.75</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2782,7 +2782,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27586371</x:v>
+        <x:v>9870847</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2861,7 +2861,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20795529</x:v>
+        <x:v>1813346</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2924,7 +2924,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19464313</x:v>
+        <x:v>2261208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2980,16 +2980,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c>
-        <x:v>36358.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1112.75</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>35245.85</x:v>
+        <x:v>36381.29</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1116.72</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>35264.57</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3011,7 +3011,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24522457</x:v>
+        <x:v>7692208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3067,16 +3067,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c>
-        <x:v>24123.04</x:v>
-      </x:c>
-      <x:c>
-        <x:v>721.53</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>23401.51</x:v>
+        <x:v>24137.87</x:v>
+      </x:c>
+      <x:c>
+        <x:v>724.12</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>23413.75</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3098,7 +3098,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29123107</x:v>
+        <x:v>12028550</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3154,16 +3154,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c>
-        <x:v>23289.25</x:v>
-      </x:c>
-      <x:c>
-        <x:v>575.62</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>22713.63</x:v>
+        <x:v>23304.75</x:v>
+      </x:c>
+      <x:c>
+        <x:v>578.33</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>22726.42</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3185,7 +3185,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26184893</x:v>
+        <x:v>2011223</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3241,16 +3241,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c>
-        <x:v>12039.82</x:v>
-      </x:c>
-      <x:c>
-        <x:v>356.96</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>11682.86</x:v>
+        <x:v>12047.1</x:v>
+      </x:c>
+      <x:c>
+        <x:v>358.24</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>11688.86</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3272,7 +3272,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19995442</x:v>
+        <x:v>2388964</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3359,7 +3359,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28838511</x:v>
+        <x:v>7621043</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3403,14 +3403,14 @@
         <x:v>362</x:v>
       </x:c>
       <x:c>
-        <x:v>20308.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>20308.2</x:v>
+        <x:v>20145.3</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>20145.3</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3432,7 +3432,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20854546</x:v>
+        <x:v>11788568</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3476,14 +3476,14 @@
         <x:v>95</x:v>
       </x:c>
       <x:c>
-        <x:v>5092</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>5092</x:v>
+        <x:v>5063.5</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>5063.5</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3505,7 +3505,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21270361</x:v>
+        <x:v>4447154</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,14 +3549,14 @@
         <x:v>404</x:v>
       </x:c>
       <x:c>
-        <x:v>18511.28</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>18511.28</x:v>
+        <x:v>18446.64</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>18446.64</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3578,7 +3578,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2573804</x:v>
+        <x:v>4959126</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3622,14 +3622,14 @@
         <x:v>541</x:v>
       </x:c>
       <x:c>
-        <x:v>17257.9</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>17257.9</x:v>
+        <x:v>16938.71</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>16938.71</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3651,7 +3651,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24616315</x:v>
+        <x:v>1103635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3695,14 +3695,14 @@
         <x:v>437</x:v>
       </x:c>
       <x:c>
-        <x:v>17497.48</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>17497.48</x:v>
+        <x:v>17471.26</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>17471.26</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3724,7 +3724,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2285647</x:v>
+        <x:v>12466552</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3797,7 +3797,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1665657</x:v>
+        <x:v>6432766</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3841,14 +3841,14 @@
         <x:v>70</x:v>
       </x:c>
       <x:c>
-        <x:v>9021.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>9021.6</x:v>
+        <x:v>9065</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>9065</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3870,7 +3870,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26142361</x:v>
+        <x:v>11527652</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3943,7 +3943,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19687795</x:v>
+        <x:v>2028520</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3987,14 +3987,14 @@
         <x:v>520</x:v>
       </x:c>
       <x:c>
-        <x:v>21138</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>21138</x:v>
+        <x:v>21054.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>21054.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -4016,7 +4016,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28731820</x:v>
+        <x:v>13151421</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4089,7 +4089,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25502563</x:v>
+        <x:v>11951345</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4133,14 +4133,14 @@
         <x:v>87</x:v>
       </x:c>
       <x:c>
-        <x:v>8254.56</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8254.56</x:v>
+        <x:v>8279.79</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8279.79</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -4162,7 +4162,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8448112</x:v>
+        <x:v>12746275</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4206,14 +4206,14 @@
         <x:v>59</x:v>
       </x:c>
       <x:c>
-        <x:v>9593.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>9593.4</x:v>
+        <x:v>9629.98</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>9629.98</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -4235,7 +4235,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7187398</x:v>
+        <x:v>12370538</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4279,14 +4279,14 @@
         <x:v>937</x:v>
       </x:c>
       <x:c>
-        <x:v>8292.45</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8292.45</x:v>
+        <x:v>8283.08</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8283.08</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -4308,7 +4308,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23051344</x:v>
+        <x:v>13921667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4352,14 +4352,14 @@
         <x:v>521</x:v>
       </x:c>
       <x:c>
-        <x:v>18073.49</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>18073.49</x:v>
+        <x:v>18016.18</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>18016.18</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -4381,7 +4381,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25890100</x:v>
+        <x:v>10121906</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4425,14 +4425,14 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c>
-        <x:v>25769.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>25769.7</x:v>
+        <x:v>26003.97</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>26003.97</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -4454,7 +4454,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24970770</x:v>
+        <x:v>5059261</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4498,14 +4498,14 @@
         <x:v>272</x:v>
       </x:c>
       <x:c>
-        <x:v>20536</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>20536</x:v>
+        <x:v>20549.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>20549.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -4527,7 +4527,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23480889</x:v>
+        <x:v>14327031</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4571,14 +4571,14 @@
         <x:v>103</x:v>
       </x:c>
       <x:c>
-        <x:v>7972.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7972.2</x:v>
+        <x:v>7941.3</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7941.3</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -4600,7 +4600,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25619867</x:v>
+        <x:v>12057284</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4665,7 +4665,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24556110</x:v>
+        <x:v>12875672</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4730,7 +4730,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29090984</x:v>
+        <x:v>8387492</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4795,7 +4795,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28423721</x:v>
+        <x:v>9068653</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4860,7 +4860,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>257104</x:v>
+        <x:v>6778224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4925,7 +4925,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20063160</x:v>
+        <x:v>2572538</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4990,7 +4990,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26902315</x:v>
+        <x:v>9627069</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5055,7 +5055,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19598769</x:v>
+        <x:v>2120456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5120,7 +5120,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19244538</x:v>
+        <x:v>3397428</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5195,7 +5195,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29169635</x:v>
+        <x:v>8225147</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5270,7 +5270,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22889983</x:v>
+        <x:v>14441615</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5349,7 +5349,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>17263810</x:v>
+        <x:v>5355510</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5428,7 +5428,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>19182203</x:v>
+        <x:v>3348503</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5507,7 +5507,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>27414276</x:v>
+        <x:v>9933981</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5586,7 +5586,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>22408875</x:v>
+        <x:v>14120700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5649,7 +5649,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24404022</x:v>
+        <x:v>12924199</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5705,16 +5705,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c>
-        <x:v>51865.62</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1173.12</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>50692.5</x:v>
+        <x:v>51894.72</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1178.94</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>50715.78</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -5736,7 +5736,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17448267</x:v>
+        <x:v>12921317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5792,16 +5792,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c>
-        <x:v>9071.65</x:v>
-      </x:c>
-      <x:c>
-        <x:v>11.28</x:v>
-      </x:c>
-      <x:c>
-        <x:v>21.49</x:v>
-      </x:c>
-      <x:c>
-        <x:v>9038.88</x:v>
+        <x:v>9076.44</x:v>
+      </x:c>
+      <x:c>
+        <x:v>13.76</x:v>
+      </x:c>
+      <x:c>
+        <x:v>15.28</x:v>
+      </x:c>
+      <x:c>
+        <x:v>9047.4</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -5823,7 +5823,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26268841</x:v>
+        <x:v>12527672</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5879,16 +5879,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c>
-        <x:v>13648.23</x:v>
-      </x:c>
-      <x:c>
-        <x:v>547.23</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>13101</x:v>
+        <x:v>13656.02</x:v>
+      </x:c>
+      <x:c>
+        <x:v>548.4</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>13107.62</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -5910,7 +5910,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20047468</x:v>
+        <x:v>1986617</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5966,16 +5966,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c>
-        <x:v>27296.47</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1094.47</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>26202</x:v>
+        <x:v>27312.05</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1096.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>26215.25</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -5997,7 +5997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2037659</x:v>
+        <x:v>5563198</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6053,16 +6053,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c>
-        <x:v>9389.88</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>9389.88</x:v>
+        <x:v>9394.61</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>9394.61</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -6084,7 +6084,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28465209</x:v>
+        <x:v>11730504</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6171,7 +6171,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23832119</x:v>
+        <x:v>12575010</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6227,16 +6227,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c>
-        <x:v>49188.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>49188.8</x:v>
+        <x:v>49211.97</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>49211.97</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -6258,7 +6258,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28346541</x:v>
+        <x:v>14484892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6345,7 +6345,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28426281</x:v>
+        <x:v>7800388</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6389,14 +6389,14 @@
         <x:v>116</x:v>
       </x:c>
       <x:c>
-        <x:v>6507.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6507.6</x:v>
+        <x:v>6455.4</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6455.4</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -6418,7 +6418,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23253988</x:v>
+        <x:v>3878208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6462,14 +6462,14 @@
         <x:v>30</x:v>
       </x:c>
       <x:c>
-        <x:v>1608</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>1608</x:v>
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>1599</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -6491,7 +6491,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28285820</x:v>
+        <x:v>11907414</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6564,7 +6564,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18553534</x:v>
+        <x:v>3176865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6637,7 +6637,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8376657</x:v>
+        <x:v>5173567</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6681,14 +6681,14 @@
         <x:v>132</x:v>
       </x:c>
       <x:c>
-        <x:v>6048.24</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6048.24</x:v>
+        <x:v>6027.12</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6027.12</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -6710,7 +6710,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24893444</x:v>
+        <x:v>14919088</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6754,14 +6754,14 @@
         <x:v>456</x:v>
       </x:c>
       <x:c>
-        <x:v>14546.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>14546.4</x:v>
+        <x:v>14277.36</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>14277.36</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -6783,7 +6783,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6063002</x:v>
+        <x:v>9316045</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6827,14 +6827,14 @@
         <x:v>135</x:v>
       </x:c>
       <x:c>
-        <x:v>5405.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>5405.4</x:v>
+        <x:v>5397.3</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>5397.3</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -6856,7 +6856,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25634563</x:v>
+        <x:v>764204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6929,7 +6929,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27279511</x:v>
+        <x:v>10061095</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6973,14 +6973,14 @@
         <x:v>61</x:v>
       </x:c>
       <x:c>
-        <x:v>7861.68</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7861.68</x:v>
+        <x:v>7899.5</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7899.5</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7002,7 +7002,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18079075</x:v>
+        <x:v>3707134</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7075,7 +7075,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23389406</x:v>
+        <x:v>13967987</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7148,7 +7148,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25370709</x:v>
+        <x:v>12028121</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7192,14 +7192,14 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c>
-        <x:v>15490.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>15490.7</x:v>
+        <x:v>15431.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>15431.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7221,7 +7221,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23744932</x:v>
+        <x:v>13986076</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7265,14 +7265,14 @@
         <x:v>337</x:v>
       </x:c>
       <x:c>
-        <x:v>13699.05</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>13699.05</x:v>
+        <x:v>13645.13</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>13645.13</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7294,7 +7294,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24255600</x:v>
+        <x:v>11006583</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7338,14 +7338,14 @@
         <x:v>122</x:v>
       </x:c>
       <x:c>
-        <x:v>47575.12</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>47575.12</x:v>
+        <x:v>47512.9</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>47512.9</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7367,7 +7367,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23503166</x:v>
+        <x:v>2361341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7440,7 +7440,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19871135</x:v>
+        <x:v>2861049</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7513,7 +7513,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>563087</x:v>
+        <x:v>7625961</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7586,7 +7586,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>504854</x:v>
+        <x:v>7571459</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7630,14 +7630,14 @@
         <x:v>80</x:v>
       </x:c>
       <x:c>
-        <x:v>7590.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7590.4</x:v>
+        <x:v>7613.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7613.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7659,7 +7659,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23307936</x:v>
+        <x:v>6248183</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7732,7 +7732,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21225248</x:v>
+        <x:v>570235</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7776,14 +7776,14 @@
         <x:v>52</x:v>
       </x:c>
       <x:c>
-        <x:v>8455.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8455.2</x:v>
+        <x:v>8487.44</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8487.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7805,7 +7805,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17379461</x:v>
+        <x:v>12990687</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7849,14 +7849,14 @@
         <x:v>857</x:v>
       </x:c>
       <x:c>
-        <x:v>7584.45</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7584.45</x:v>
+        <x:v>7575.88</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7575.88</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7878,7 +7878,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20310209</x:v>
+        <x:v>1950643</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7922,14 +7922,14 @@
         <x:v>170</x:v>
       </x:c>
       <x:c>
-        <x:v>5897.3</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>5897.3</x:v>
+        <x:v>5878.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>5878.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7951,7 +7951,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22093764</x:v>
+        <x:v>14133953</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7995,14 +7995,14 @@
         <x:v>2754</x:v>
       </x:c>
       <x:c>
-        <x:v>48745.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>48745.8</x:v>
+        <x:v>48690.72</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>48690.72</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8024,7 +8024,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22408893</x:v>
+        <x:v>14496149</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8068,14 +8068,14 @@
         <x:v>4582</x:v>
       </x:c>
       <x:c>
-        <x:v>45361.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>45361.8</x:v>
+        <x:v>45774.18</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>45774.18</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8097,7 +8097,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25120233</x:v>
+        <x:v>5641536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8170,7 +8170,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26980307</x:v>
+        <x:v>10249549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8214,14 +8214,14 @@
         <x:v>290</x:v>
       </x:c>
       <x:c>
-        <x:v>21895</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>21895</x:v>
+        <x:v>21909.5</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>21909.5</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8243,7 +8243,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19660455</x:v>
+        <x:v>3559443</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8287,14 +8287,14 @@
         <x:v>94</x:v>
       </x:c>
       <x:c>
-        <x:v>7275.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7275.6</x:v>
+        <x:v>7247.4</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7247.4</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8316,7 +8316,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17401089</x:v>
+        <x:v>5646881</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8381,7 +8381,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21684347</x:v>
+        <x:v>1014354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8446,7 +8446,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21329822</x:v>
+        <x:v>344725</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8511,7 +8511,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20178092</x:v>
+        <x:v>1523265</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8576,7 +8576,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25763525</x:v>
+        <x:v>10567208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8641,7 +8641,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22371187</x:v>
+        <x:v>14922061</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8706,7 +8706,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23319413</x:v>
+        <x:v>14155882</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8771,7 +8771,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1522718</x:v>
+        <x:v>5891975</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8836,7 +8836,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26398220</x:v>
+        <x:v>9911134</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8901,7 +8901,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20032008</x:v>
+        <x:v>2580606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8966,7 +8966,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26878139</x:v>
+        <x:v>10358019</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9031,7 +9031,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25306450</x:v>
+        <x:v>11974003</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9096,7 +9096,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27568936</x:v>
+        <x:v>8712061</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9161,7 +9161,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25622314</x:v>
+        <x:v>10716447</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9236,7 +9236,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>181803</x:v>
+        <x:v>6983675</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9311,7 +9311,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19128413</x:v>
+        <x:v>3498853</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9355,16 +9355,16 @@
         <x:v>139.8694019</x:v>
       </x:c>
       <x:c>
-        <x:v>3129.12</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>3129.12</x:v>
+        <x:v>3107.74</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>3107.74</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9386,7 +9386,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17746128</x:v>
+        <x:v>4132741</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9461,7 +9461,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26948961</x:v>
+        <x:v>10396266</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9505,16 +9505,16 @@
         <x:v>34106.70861</x:v>
       </x:c>
       <x:c>
-        <x:v>70345.18</x:v>
-      </x:c>
-      <x:c>
-        <x:v>759.1</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>69586.08</x:v>
+        <x:v>70363.55</x:v>
+      </x:c>
+      <x:c>
+        <x:v>762.77</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>69600.78</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9536,7 +9536,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23121153</x:v>
+        <x:v>13423841</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9580,16 +9580,16 @@
         <x:v>10784.950882</x:v>
       </x:c>
       <x:c>
-        <x:v>20063.89</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>20063.89</x:v>
+        <x:v>19967.48</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>19967.48</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9611,7 +9611,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19904844</x:v>
+        <x:v>2703761</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9655,16 +9655,16 @@
         <x:v>24803.64275</x:v>
       </x:c>
       <x:c>
-        <x:v>42851.01</x:v>
-      </x:c>
-      <x:c>
-        <x:v>324.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>42526.21</x:v>
+        <x:v>42748.73</x:v>
+      </x:c>
+      <x:c>
+        <x:v>303.42</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>42445.31</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9686,7 +9686,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23949476</x:v>
+        <x:v>12456032</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9761,7 +9761,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19369471</x:v>
+        <x:v>2315861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9836,7 +9836,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27693752</x:v>
+        <x:v>8587951</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9915,7 +9915,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>27258473</x:v>
+        <x:v>10074353</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9994,7 +9994,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>24842852</x:v>
+        <x:v>11536746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10069,7 +10069,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24543149</x:v>
+        <x:v>12777178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10144,7 +10144,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21629112</x:v>
+        <x:v>956472</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10207,7 +10207,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16074103</x:v>
+        <x:v>22081628</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10263,16 +10263,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c>
-        <x:v>102262.28</x:v>
-      </x:c>
-      <x:c>
-        <x:v>3895.89</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>98366.39</x:v>
+        <x:v>102313.32</x:v>
+      </x:c>
+      <x:c>
+        <x:v>3904.83</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>98408.49</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10294,7 +10294,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14449268</x:v>
+        <x:v>17327413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10350,16 +10350,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c>
-        <x:v>8533.3</x:v>
-      </x:c>
-      <x:c>
-        <x:v>119.99</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>8413.31</x:v>
+        <x:v>8538.05</x:v>
+      </x:c>
+      <x:c>
+        <x:v>121.06</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>8416.99</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10381,7 +10381,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13630952</x:v>
+        <x:v>17612020</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10437,16 +10437,16 @@
         <x:v>67</x:v>
       </x:c>
       <x:c>
-        <x:v>81783.21</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2587.06</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>79196.15</x:v>
+        <x:v>81831.57</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2595.52</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>79236.05</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10468,7 +10468,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3296803</x:v>
+        <x:v>18843297</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10524,16 +10524,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c>
-        <x:v>146980.92</x:v>
-      </x:c>
-      <x:c>
-        <x:v>4721.66</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>142259.26</x:v>
+        <x:v>147071.12</x:v>
+      </x:c>
+      <x:c>
+        <x:v>4737.44</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>142333.68</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10555,7 +10555,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15952160</x:v>
+        <x:v>28269316</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10611,16 +10611,16 @@
         <x:v>67</x:v>
       </x:c>
       <x:c>
-        <x:v>81038.41</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2456.72</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>78581.69</x:v>
+        <x:v>81084.67</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2464.81</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>78619.86</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10642,7 +10642,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6606853</x:v>
+        <x:v>21338719</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10686,14 +10686,14 @@
         <x:v>455</x:v>
       </x:c>
       <x:c>
-        <x:v>25525.5</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>25525.5</x:v>
+        <x:v>25320.75</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>25320.75</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10715,7 +10715,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6556422</x:v>
+        <x:v>28134166</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10759,14 +10759,14 @@
         <x:v>119</x:v>
       </x:c>
       <x:c>
-        <x:v>6378.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6378.4</x:v>
+        <x:v>6342.7</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6342.7</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10788,7 +10788,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6421519</x:v>
+        <x:v>20576657</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10832,14 +10832,14 @@
         <x:v>605</x:v>
       </x:c>
       <x:c>
-        <x:v>27721.1</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>27721.1</x:v>
+        <x:v>27624.3</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>27624.3</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10861,7 +10861,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3494545</x:v>
+        <x:v>20548913</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10905,14 +10905,14 @@
         <x:v>851</x:v>
       </x:c>
       <x:c>
-        <x:v>27146.9</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>27146.9</x:v>
+        <x:v>26644.81</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>26644.81</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10934,7 +10934,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12304278</x:v>
+        <x:v>15398947</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10978,14 +10978,14 @@
         <x:v>710</x:v>
       </x:c>
       <x:c>
-        <x:v>28428.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>28428.4</x:v>
+        <x:v>28385.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>28385.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11007,7 +11007,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9879732</x:v>
+        <x:v>18290210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11080,7 +11080,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7291903</x:v>
+        <x:v>15690884</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11124,14 +11124,14 @@
         <x:v>300</x:v>
       </x:c>
       <x:c>
-        <x:v>38664</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>38664</x:v>
+        <x:v>38850</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>38850</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11153,7 +11153,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8893046</x:v>
+        <x:v>21379515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11226,7 +11226,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11326037</x:v>
+        <x:v>26713713</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11270,14 +11270,14 @@
         <x:v>793</x:v>
       </x:c>
       <x:c>
-        <x:v>32235.45</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>32235.45</x:v>
+        <x:v>32108.57</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>32108.57</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11299,7 +11299,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6398164</x:v>
+        <x:v>18335028</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11343,14 +11343,14 @@
         <x:v>400</x:v>
       </x:c>
       <x:c>
-        <x:v>37952</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>37952</x:v>
+        <x:v>38068</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>38068</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11372,7 +11372,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13344523</x:v>
+        <x:v>17877255</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11416,14 +11416,14 @@
         <x:v>259</x:v>
       </x:c>
       <x:c>
-        <x:v>42113.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>42113.4</x:v>
+        <x:v>42273.98</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>42273.98</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11445,7 +11445,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5517546</x:v>
+        <x:v>24852231</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11489,14 +11489,14 @@
         <x:v>4162</x:v>
       </x:c>
       <x:c>
-        <x:v>36833.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>36833.7</x:v>
+        <x:v>36792.08</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>36792.08</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11518,7 +11518,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7828777</x:v>
+        <x:v>15754664</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11562,14 +11562,14 @@
         <x:v>817</x:v>
       </x:c>
       <x:c>
-        <x:v>28341.73</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>28341.73</x:v>
+        <x:v>28251.86</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>28251.86</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11591,7 +11591,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4790425</x:v>
+        <x:v>19682014</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11635,14 +11635,14 @@
         <x:v>3593</x:v>
       </x:c>
       <x:c>
-        <x:v>35570.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>35570.7</x:v>
+        <x:v>35894.07</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>35894.07</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11664,7 +11664,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10170546</x:v>
+        <x:v>20526212</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11737,7 +11737,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13441041</x:v>
+        <x:v>24638425</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11781,14 +11781,14 @@
         <x:v>424</x:v>
       </x:c>
       <x:c>
-        <x:v>32012</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>32012</x:v>
+        <x:v>32033.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>32033.2</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11810,7 +11810,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3751055</x:v>
+        <x:v>18622761</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11854,14 +11854,14 @@
         <x:v>456</x:v>
       </x:c>
       <x:c>
-        <x:v>35294.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>35294.4</x:v>
+        <x:v>35157.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>35157.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11883,7 +11883,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9007469</x:v>
+        <x:v>14907281</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11948,7 +11948,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5632891</x:v>
+        <x:v>17409859</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12013,7 +12013,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2423793</x:v>
+        <x:v>20299316</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12078,7 +12078,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1360042</x:v>
+        <x:v>20973109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12143,7 +12143,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15708704</x:v>
+        <x:v>23204148</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12208,7 +12208,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12421390</x:v>
+        <x:v>25529546</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12273,7 +12273,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4954744</x:v>
+        <x:v>18857748</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12338,7 +12338,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12894293</x:v>
+        <x:v>25962424</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12403,7 +12403,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9375964</x:v>
+        <x:v>28429311</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12468,7 +12468,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11658654</x:v>
+        <x:v>26297789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12543,7 +12543,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16452264</x:v>
+        <x:v>22599338</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12618,7 +12618,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8218687</x:v>
+        <x:v>13513496</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12693,7 +12693,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12870340</x:v>
+        <x:v>26098577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12756,7 +12756,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2521960</x:v>
+        <x:v>6183027</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12831,7 +12831,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18010707</x:v>
+        <x:v>4493391</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12894,7 +12894,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18312896</x:v>
+        <x:v>4308447</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12950,16 +12950,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c>
-        <x:v>85511.33</x:v>
-      </x:c>
-      <x:c>
-        <x:v>5326.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>80184.63</x:v>
+        <x:v>85557.88</x:v>
+      </x:c>
+      <x:c>
+        <x:v>5333.68</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>80224.2</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12981,7 +12981,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18743803</x:v>
+        <x:v>7772538</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13037,16 +13037,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c>
-        <x:v>187318.41</x:v>
-      </x:c>
-      <x:c>
-        <x:v>7097.76</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>180220.65</x:v>
+        <x:v>187440.9</x:v>
+      </x:c>
+      <x:c>
+        <x:v>7116.13</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>180324.77</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -13068,7 +13068,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21700004</x:v>
+        <x:v>9101107</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13155,7 +13155,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28405166</x:v>
+        <x:v>9087355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13211,16 +13211,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c>
-        <x:v>29320.82</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>29320.82</x:v>
+        <x:v>29332.08</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>29332.08</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -13242,7 +13242,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25881152</x:v>
+        <x:v>2383213</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13329,7 +13329,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17625809</x:v>
+        <x:v>4072386</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13416,7 +13416,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28302228</x:v>
+        <x:v>9181454</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13503,7 +13503,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28571879</x:v>
+        <x:v>8922216</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13590,7 +13590,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26300144</x:v>
+        <x:v>11051207</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13677,7 +13677,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25356436</x:v>
+        <x:v>11986196</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13764,7 +13764,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28225703</x:v>
+        <x:v>9136774</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13851,7 +13851,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23067266</x:v>
+        <x:v>13448629</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13938,7 +13938,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28983186</x:v>
+        <x:v>7485472</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14025,7 +14025,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25460195</x:v>
+        <x:v>11879130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14112,7 +14112,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17916859</x:v>
+        <x:v>4590583</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14199,7 +14199,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18733039</x:v>
+        <x:v>2857376</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14286,7 +14286,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20012629</x:v>
+        <x:v>2622067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14373,7 +14373,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20724844</x:v>
+        <x:v>1886006</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14460,7 +14460,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>352876</x:v>
+        <x:v>6559560</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14547,7 +14547,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23535260</x:v>
+        <x:v>13904612</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14634,7 +14634,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19701485</x:v>
+        <x:v>2016315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14721,7 +14721,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17959826</x:v>
+        <x:v>4665351</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14777,16 +14777,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c>
-        <x:v>89660.39</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>89660.39</x:v>
+        <x:v>89708.56</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>89708.56</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -14808,7 +14808,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29035350</x:v>
+        <x:v>1551350</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14895,7 +14895,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18662581</x:v>
+        <x:v>3041502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14982,7 +14982,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8782131</x:v>
+        <x:v>4698383</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15069,7 +15069,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23698738</x:v>
+        <x:v>13627152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15156,7 +15156,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28091051</x:v>
+        <x:v>8459294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15243,7 +15243,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17752657</x:v>
+        <x:v>3828641</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15330,7 +15330,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28283235</x:v>
+        <x:v>9193790</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15374,14 +15374,14 @@
         <x:v>600</x:v>
       </x:c>
       <x:c>
-        <x:v>12666</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>12666</x:v>
+        <x:v>12600</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>12600</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15403,7 +15403,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18104477</x:v>
+        <x:v>11233278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15447,14 +15447,14 @@
         <x:v>140</x:v>
       </x:c>
       <x:c>
-        <x:v>7854</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7854</x:v>
+        <x:v>7791</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7791</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15476,7 +15476,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>757615</x:v>
+        <x:v>9996313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15520,14 +15520,14 @@
         <x:v>36</x:v>
       </x:c>
       <x:c>
-        <x:v>1929.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>1929.6</x:v>
+        <x:v>1918.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>1918.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15549,7 +15549,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22518994</x:v>
+        <x:v>11129707</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15593,14 +15593,14 @@
         <x:v>161</x:v>
       </x:c>
       <x:c>
-        <x:v>2629.13</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>2629.13</x:v>
+        <x:v>2606.59</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>2606.59</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15622,7 +15622,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27074</x:v>
+        <x:v>13248118</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15666,14 +15666,14 @@
         <x:v>200</x:v>
       </x:c>
       <x:c>
-        <x:v>4684</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>4684</x:v>
+        <x:v>4654</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>4654</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15695,7 +15695,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22286703</x:v>
+        <x:v>11016727</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15739,14 +15739,14 @@
         <x:v>190</x:v>
       </x:c>
       <x:c>
-        <x:v>16049.3</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>16049.3</x:v>
+        <x:v>16055</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>16055</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15768,7 +15768,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18261012</x:v>
+        <x:v>12165185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15812,14 +15812,14 @@
         <x:v>56</x:v>
       </x:c>
       <x:c>
-        <x:v>2957.36</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>2957.36</x:v>
+        <x:v>2953.44</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>2953.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15841,7 +15841,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20357731</x:v>
+        <x:v>6168579</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15885,14 +15885,14 @@
         <x:v>1560</x:v>
       </x:c>
       <x:c>
-        <x:v>19297.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>19297.2</x:v>
+        <x:v>19094.4</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>19094.4</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15914,7 +15914,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25496628</x:v>
+        <x:v>2917114</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15958,14 +15958,14 @@
         <x:v>501</x:v>
       </x:c>
       <x:c>
-        <x:v>22955.82</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>22955.82</x:v>
+        <x:v>22875.66</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>22875.66</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15987,7 +15987,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24838086</x:v>
+        <x:v>14561892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16031,14 +16031,14 @@
         <x:v>1300</x:v>
       </x:c>
       <x:c>
-        <x:v>19370</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>19370</x:v>
+        <x:v>19279</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>19279</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -16060,7 +16060,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20204232</x:v>
+        <x:v>13880413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16104,14 +16104,14 @@
         <x:v>263</x:v>
       </x:c>
       <x:c>
-        <x:v>8389.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8389.7</x:v>
+        <x:v>8234.53</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8234.53</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -16133,7 +16133,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22055170</x:v>
+        <x:v>3631088</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16177,14 +16177,14 @@
         <x:v>231</x:v>
       </x:c>
       <x:c>
-        <x:v>9249.24</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>9249.24</x:v>
+        <x:v>9235.38</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>9235.38</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -16206,7 +16206,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4757338</x:v>
+        <x:v>13645844</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16250,14 +16250,14 @@
         <x:v>1320</x:v>
       </x:c>
       <x:c>
-        <x:v>23271.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>23271.6</x:v>
+        <x:v>23034</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>23034</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -16279,7 +16279,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2747378</x:v>
+        <x:v>2426662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16352,7 +16352,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9086528</x:v>
+        <x:v>4761827</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16396,14 +16396,14 @@
         <x:v>73</x:v>
       </x:c>
       <x:c>
-        <x:v>9408.24</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>9408.24</x:v>
+        <x:v>9453.5</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>9453.5</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -16425,7 +16425,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>201994</x:v>
+        <x:v>341100</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16498,7 +16498,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20272791</x:v>
+        <x:v>1295460</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16571,7 +16571,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18653591</x:v>
+        <x:v>3049124</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16615,14 +16615,14 @@
         <x:v>1252</x:v>
       </x:c>
       <x:c>
-        <x:v>16463.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>16463.8</x:v>
+        <x:v>16401.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>16401.2</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -16644,7 +16644,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26438248</x:v>
+        <x:v>7889894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16688,14 +16688,14 @@
         <x:v>262</x:v>
       </x:c>
       <x:c>
-        <x:v>10650.3</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>10650.3</x:v>
+        <x:v>10608.38</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>10608.38</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -16717,7 +16717,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26065639</x:v>
+        <x:v>12359445</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16761,14 +16761,14 @@
         <x:v>153</x:v>
       </x:c>
       <x:c>
-        <x:v>59663.88</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>59663.88</x:v>
+        <x:v>59585.85</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>59585.85</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -16790,7 +16790,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1381520</x:v>
+        <x:v>10079829</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16863,7 +16863,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19677905</x:v>
+        <x:v>2044025</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16936,7 +16936,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25531295</x:v>
+        <x:v>11920667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16980,14 +16980,14 @@
         <x:v>100</x:v>
       </x:c>
       <x:c>
-        <x:v>9488</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>9488</x:v>
+        <x:v>9517</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>9517</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17009,7 +17009,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28357756</x:v>
+        <x:v>1186298</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17053,14 +17053,14 @@
         <x:v>62</x:v>
       </x:c>
       <x:c>
-        <x:v>10081.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>10081.2</x:v>
+        <x:v>10119.64</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>10119.64</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17082,7 +17082,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25411276</x:v>
+        <x:v>4545747</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17126,14 +17126,14 @@
         <x:v>991</x:v>
       </x:c>
       <x:c>
-        <x:v>8770.35</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8770.35</x:v>
+        <x:v>8760.44</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8760.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17155,7 +17155,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18778615</x:v>
+        <x:v>3359844</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17199,14 +17199,14 @@
         <x:v>236</x:v>
       </x:c>
       <x:c>
-        <x:v>8186.84</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8186.84</x:v>
+        <x:v>8160.88</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8160.88</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17228,7 +17228,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18932512</x:v>
+        <x:v>2299980</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17272,14 +17272,14 @@
         <x:v>3696</x:v>
       </x:c>
       <x:c>
-        <x:v>65419.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>65419.2</x:v>
+        <x:v>65345.28</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>65345.28</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17301,7 +17301,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19533481</x:v>
+        <x:v>2422002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17345,14 +17345,14 @@
         <x:v>45</x:v>
       </x:c>
       <x:c>
-        <x:v>2156.85</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>2156.85</x:v>
+        <x:v>2135.25</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>2135.25</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17374,7 +17374,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>862613</x:v>
+        <x:v>9107064</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17418,14 +17418,14 @@
         <x:v>965</x:v>
       </x:c>
       <x:c>
-        <x:v>9553.5</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>9553.5</x:v>
+        <x:v>9640.35</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>9640.35</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17447,7 +17447,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18938419</x:v>
+        <x:v>10130576</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17520,7 +17520,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24536641</x:v>
+        <x:v>12783978</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17564,14 +17564,14 @@
         <x:v>600</x:v>
       </x:c>
       <x:c>
-        <x:v>24708</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>24708</x:v>
+        <x:v>24498</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>24498</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17593,7 +17593,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26345424</x:v>
+        <x:v>6199398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17637,14 +17637,14 @@
         <x:v>440</x:v>
       </x:c>
       <x:c>
-        <x:v>25269.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>25269.2</x:v>
+        <x:v>25784</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>25784</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17666,7 +17666,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25142941</x:v>
+        <x:v>4987734</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17710,14 +17710,14 @@
         <x:v>426</x:v>
       </x:c>
       <x:c>
-        <x:v>32163</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>32163</x:v>
+        <x:v>32184.3</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>32184.3</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17739,7 +17739,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2057776</x:v>
+        <x:v>6894548</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17783,14 +17783,14 @@
         <x:v>107</x:v>
       </x:c>
       <x:c>
-        <x:v>8281.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8281.8</x:v>
+        <x:v>8249.7</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8249.7</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17812,7 +17812,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24882817</x:v>
+        <x:v>11283467</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17856,14 +17856,14 @@
         <x:v>33</x:v>
       </x:c>
       <x:c>
-        <x:v>1518</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>1518</x:v>
+        <x:v>1513.95</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>1513.95</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17885,7 +17885,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18080189</x:v>
+        <x:v>10361709</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17950,7 +17950,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18808623</x:v>
+        <x:v>3695688</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18015,7 +18015,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17455475</x:v>
+        <x:v>4125012</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18080,7 +18080,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27660562</x:v>
+        <x:v>8755419</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18145,7 +18145,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28490104</x:v>
+        <x:v>8886199</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18210,7 +18210,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17836139</x:v>
+        <x:v>3861968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18275,7 +18275,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2075727</x:v>
+        <x:v>6393734</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18340,7 +18340,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29125928</x:v>
+        <x:v>8197793</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18405,7 +18405,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27195936</x:v>
+        <x:v>10146931</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18470,7 +18470,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28502953</x:v>
+        <x:v>8875894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18535,7 +18535,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25864078</x:v>
+        <x:v>10681415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18600,7 +18600,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26991164</x:v>
+        <x:v>9546247</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18665,7 +18665,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18164896</x:v>
+        <x:v>4450059</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18730,7 +18730,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17212454</x:v>
+        <x:v>5297029</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18795,7 +18795,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24082667</x:v>
+        <x:v>12317479</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18860,7 +18860,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20483411</x:v>
+        <x:v>1200545</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18925,7 +18925,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28332676</x:v>
+        <x:v>9154333</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18990,7 +18990,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20968890</x:v>
+        <x:v>1645596</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19055,7 +19055,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26708965</x:v>
+        <x:v>9712871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19120,7 +19120,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25421557</x:v>
+        <x:v>12034455</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19185,7 +19185,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>500451</x:v>
+        <x:v>7462395</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19250,7 +19250,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19348547</x:v>
+        <x:v>2371416</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19315,7 +19315,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21535957</x:v>
+        <x:v>189450</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19390,7 +19390,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>958939</x:v>
+        <x:v>5987372</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19434,16 +19434,16 @@
         <x:v>27988.6523821</x:v>
       </x:c>
       <x:c>
-        <x:v>143638.58</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1649.04</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>141989.54</x:v>
+        <x:v>143718.08</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1664.94</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>142053.14</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19465,7 +19465,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3797426</x:v>
+        <x:v>5086481</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19540,7 +19540,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26356758</x:v>
+        <x:v>11111202</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19619,7 +19619,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>21731992</x:v>
+        <x:v>883095</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19694,7 +19694,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19333009</x:v>
+        <x:v>2387838</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19773,7 +19773,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>26951519</x:v>
+        <x:v>9465502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19848,7 +19848,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4265903</x:v>
+        <x:v>5081853</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19892,16 +19892,16 @@
         <x:v>33808.77064958</x:v>
       </x:c>
       <x:c>
-        <x:v>35080.71</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>20.98</x:v>
-      </x:c>
-      <x:c>
-        <x:v>35059.73</x:v>
+        <x:v>35002.3</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0.53</x:v>
+      </x:c>
+      <x:c>
+        <x:v>35001.77</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19923,7 +19923,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>554462</x:v>
+        <x:v>7295392</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19960,33 +19960,33 @@
       <x:c s="9"/>
       <x:c s="8"/>
       <x:c>
-        <x:v>1943.18</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1943.18</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>1943.18</x:v>
-      </x:c>
-      <x:c/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>M2WM MFO SERVICOS ADMINISTRATIVOS LTDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>-</x:t>
-        </x:is>
-      </x:c>
-      <x:c/>
-      <x:c s="10">
-        <x:v>10293500</x:v>
+        <x:v>1793.48</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1793.48</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>1793.48</x:v>
+      </x:c>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>M2WM MFO SERVICOS ADMINISTRATIVOS LTDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>-</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c s="10">
+        <x:v>21145905</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20042,16 +20042,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c>
-        <x:v>15246.28</x:v>
-      </x:c>
-      <x:c>
-        <x:v>393.1</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>14853.18</x:v>
+        <x:v>15255.18</x:v>
+      </x:c>
+      <x:c>
+        <x:v>394.65</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>14860.53</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20073,7 +20073,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13598319</x:v>
+        <x:v>20203002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20129,16 +20129,16 @@
         <x:v>198</x:v>
       </x:c>
       <x:c>
-        <x:v>234557.97</x:v>
-      </x:c>
-      <x:c>
-        <x:v>6397.64</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>228160.33</x:v>
+        <x:v>234698.29</x:v>
+      </x:c>
+      <x:c>
+        <x:v>6422.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>228276.09</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20160,7 +20160,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10958554</x:v>
+        <x:v>20907349</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20216,16 +20216,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c>
-        <x:v>38643.86</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1512.67</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>37131.19</x:v>
+        <x:v>38667.98</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1516.89</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>37151.09</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20247,7 +20247,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6248143</x:v>
+        <x:v>18126292</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20303,16 +20303,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c>
-        <x:v>3824.46</x:v>
-      </x:c>
-      <x:c>
-        <x:v>144.28</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>3680.18</x:v>
+        <x:v>3826.85</x:v>
+      </x:c>
+      <x:c>
+        <x:v>144.69</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>3682.16</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20334,7 +20334,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16514377</x:v>
+        <x:v>20730047</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20390,16 +20390,16 @@
         <x:v>195</x:v>
       </x:c>
       <x:c>
-        <x:v>233920.55</x:v>
-      </x:c>
-      <x:c>
-        <x:v>6811.09</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>227109.46</x:v>
+        <x:v>234031.14</x:v>
+      </x:c>
+      <x:c>
+        <x:v>6830.45</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>227200.69</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20421,7 +20421,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8918207</x:v>
+        <x:v>22704832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20477,16 +20477,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c>
-        <x:v>9748.49</x:v>
-      </x:c>
-      <x:c>
-        <x:v>305.98</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>9442.51</x:v>
+        <x:v>9752.5</x:v>
+      </x:c>
+      <x:c>
+        <x:v>306.68</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>9445.82</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20508,7 +20508,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6439773</x:v>
+        <x:v>22605629</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20564,16 +20564,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c>
-        <x:v>9830.96</x:v>
-      </x:c>
-      <x:c>
-        <x:v>320.41</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>9510.55</x:v>
+        <x:v>9835.51</x:v>
+      </x:c>
+      <x:c>
+        <x:v>321.21</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>9514.3</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20595,7 +20595,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4331057</x:v>
+        <x:v>24777251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20651,16 +20651,16 @@
         <x:v>98</x:v>
       </x:c>
       <x:c>
-        <x:v>115899.96</x:v>
-      </x:c>
-      <x:c>
-        <x:v>3132.49</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>112767.47</x:v>
+        <x:v>115970.62</x:v>
+      </x:c>
+      <x:c>
+        <x:v>3144.85</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>112825.77</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20682,7 +20682,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14179705</x:v>
+        <x:v>26715487</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20738,16 +20738,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c>
-        <x:v>3594.41</x:v>
-      </x:c>
-      <x:c>
-        <x:v>104.02</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>3490.39</x:v>
+        <x:v>3595.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>104.26</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>3491.54</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20769,7 +20769,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15917864</x:v>
+        <x:v>16041303</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20825,16 +20825,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c>
-        <x:v>36238.19</x:v>
-      </x:c>
-      <x:c>
-        <x:v>647.63</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>35590.56</x:v>
+        <x:v>36262.55</x:v>
+      </x:c>
+      <x:c>
+        <x:v>652.51</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>35610.04</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20856,7 +20856,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14268029</x:v>
+        <x:v>19238429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20912,16 +20912,16 @@
         <x:v>206</x:v>
       </x:c>
       <x:c>
-        <x:v>245944.03</x:v>
-      </x:c>
-      <x:c>
-        <x:v>6990.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>238953.83</x:v>
+        <x:v>246057.27</x:v>
+      </x:c>
+      <x:c>
+        <x:v>7010.02</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>239047.25</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20943,7 +20943,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5433109</x:v>
+        <x:v>20226659</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20999,16 +20999,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c>
-        <x:v>4816.37</x:v>
-      </x:c>
-      <x:c>
-        <x:v>142.86</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>4673.51</x:v>
+        <x:v>4818.49</x:v>
+      </x:c>
+      <x:c>
+        <x:v>143.23</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>4675.26</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21030,7 +21030,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12980286</x:v>
+        <x:v>29119541</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21086,16 +21086,16 @@
         <x:v>170</x:v>
       </x:c>
       <x:c>
-        <x:v>204650.26</x:v>
-      </x:c>
-      <x:c>
-        <x:v>6063.79</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>198586.47</x:v>
+        <x:v>204748.89</x:v>
+      </x:c>
+      <x:c>
+        <x:v>6081.05</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>198667.84</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21117,7 +21117,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4899902</x:v>
+        <x:v>26366083</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21173,16 +21173,16 @@
         <x:v>170</x:v>
       </x:c>
       <x:c>
-        <x:v>205342.95</x:v>
-      </x:c>
-      <x:c>
-        <x:v>6185.01</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>199157.94</x:v>
+        <x:v>205443.71</x:v>
+      </x:c>
+      <x:c>
+        <x:v>6202.65</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>199241.06</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21204,181 +21204,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12149291</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>004466342</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Tatyana</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Renda Fixa</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>BANCARIO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>LCA-25C04922575</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>LCA</x:t>
-        </x:is>
-      </x:c>
-      <x:c/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>BANCO BOCOM BBM S.A.</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45743</x:v>
-      </x:c>
-      <x:c>
-        <x:v>13.05</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>13.05</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c>
-        <x:v>50</x:v>
-      </x:c>
-      <x:c>
-        <x:v>56387.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>56387.6</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Pré-fixado</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>M2WM MFO SERVICOS ADMINISTRATIVOS LTDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>-</x:t>
-        </x:is>
-      </x:c>
-      <x:c/>
-      <x:c s="10">
-        <x:v>9616437</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>004466342</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Tatyana</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Renda Fixa</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>BANCARIO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>LCA-25C04014086</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>LCA</x:t>
-        </x:is>
-      </x:c>
-      <x:c/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>BANCO BTG PACTUAL S A</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45737</x:v>
-      </x:c>
-      <x:c>
-        <x:v>12.47</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>12.47</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c>
-        <x:v>8431.31</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>8431.31</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Pré-fixado</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>M2WM MFO SERVICOS ADMINISTRATIVOS LTDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>-</x:t>
-        </x:is>
-      </x:c>
-      <x:c/>
-      <x:c s="10">
-        <x:v>6705797</x:v>
+        <x:v>23874085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21465,7 +21291,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13091742</x:v>
+        <x:v>23998284</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21521,16 +21347,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c>
-        <x:v>116252.78</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>116252.78</x:v>
+        <x:v>116312.71</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>116312.71</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21552,7 +21378,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14077412</x:v>
+        <x:v>21146084</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21608,16 +21434,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c>
-        <x:v>26800.39</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>26800.39</x:v>
+        <x:v>26814.28</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>26814.28</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21639,7 +21465,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7986260</x:v>
+        <x:v>16478539</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21695,16 +21521,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c>
-        <x:v>69471.73</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>69471.73</x:v>
+        <x:v>69507.74</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>69507.74</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21726,7 +21552,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14038477</x:v>
+        <x:v>18102758</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21782,16 +21608,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c>
-        <x:v>66456.18</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>66456.18</x:v>
+        <x:v>66489.81</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>66489.81</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21813,7 +21639,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7435137</x:v>
+        <x:v>25397297</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21869,16 +21695,16 @@
         <x:v>150000</x:v>
       </x:c>
       <x:c>
-        <x:v>175957.58</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>175957.58</x:v>
+        <x:v>176049.25</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>176049.25</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21900,7 +21726,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8938793</x:v>
+        <x:v>16760344</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21973,7 +21799,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16476300</x:v>
+        <x:v>23657986</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22014,10 +21840,10 @@
       <x:c s="9"/>
       <x:c s="8"/>
       <x:c>
-        <x:v>117374.924284209</x:v>
-      </x:c>
-      <x:c>
-        <x:v>416003.04</x:v>
+        <x:v>135714.622199337</x:v>
+      </x:c>
+      <x:c>
+        <x:v>481003.04</x:v>
       </x:c>
       <x:c>
         <x:v>264.11</x:v>
@@ -22026,7 +21852,7 @@
         <x:v>1077.3</x:v>
       </x:c>
       <x:c>
-        <x:v>414661.63</x:v>
+        <x:v>479661.63</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22048,7 +21874,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10142555</x:v>
+        <x:v>27712708</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22092,16 +21918,16 @@
         <x:v>32490.4059374</x:v>
       </x:c>
       <x:c>
-        <x:v>60735.11</x:v>
-      </x:c>
-      <x:c>
-        <x:v>251.58</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>60483.53</x:v>
+        <x:v>60745.71</x:v>
+      </x:c>
+      <x:c>
+        <x:v>253.96</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>60491.75</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22123,7 +21949,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14448901</x:v>
+        <x:v>25615987</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22186,7 +22012,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26828721</x:v>
+        <x:v>9583073</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22265,7 +22091,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>18831670</x:v>
+        <x:v>3678693</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22328,7 +22154,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17569113</x:v>
+        <x:v>4014920</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22407,7 +22233,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>28834182</x:v>
+        <x:v>7631111</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22470,7 +22296,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25612847</x:v>
+        <x:v>11845736</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22514,16 +22340,16 @@
         <x:v>0.4929942</x:v>
       </x:c>
       <x:c>
-        <x:v>409.12</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2.53</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>406.59</x:v>
+        <x:v>409.33</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2.56</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>406.77</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22545,7 +22371,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19249394</x:v>
+        <x:v>3393765</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22620,7 +22446,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28296696</x:v>
+        <x:v>9183998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22664,16 +22490,16 @@
         <x:v>8096.30276</x:v>
       </x:c>
       <x:c>
-        <x:v>26436.09</x:v>
-      </x:c>
-      <x:c>
-        <x:v>269.56</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>26166.53</x:v>
+        <x:v>26443.61</x:v>
+      </x:c>
+      <x:c>
+        <x:v>270.87</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>26172.74</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22695,7 +22521,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19613584</x:v>
+        <x:v>2107758</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22770,7 +22596,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18155061</x:v>
+        <x:v>4459699</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22845,7 +22671,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19119438</x:v>
+        <x:v>3523635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22908,7 +22734,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20386628</x:v>
+        <x:v>1300971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22981,7 +22807,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21614994</x:v>
+        <x:v>998727</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23046,7 +22872,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25769060</x:v>
+        <x:v>11694560</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23121,7 +22947,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26791012</x:v>
+        <x:v>9738436</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23196,7 +23022,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23808515</x:v>
+        <x:v>13514260</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23259,7 +23085,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2158918</x:v>
+        <x:v>21326016</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23315,16 +23141,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c>
-        <x:v>2249.95</x:v>
-      </x:c>
-      <x:c>
-        <x:v>49.99</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2199.96</x:v>
+        <x:v>2251.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>50.24</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2200.96</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23346,7 +23172,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16295528</x:v>
+        <x:v>27454916</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23402,16 +23228,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c>
-        <x:v>4406.67</x:v>
-      </x:c>
-      <x:c>
-        <x:v>81.33</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>4325.34</x:v>
+        <x:v>4409.56</x:v>
+      </x:c>
+      <x:c>
+        <x:v>81.91</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>4327.65</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23433,7 +23259,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11605223</x:v>
+        <x:v>17546037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23508,7 +23334,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13921330</x:v>
+        <x:v>25087244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23571,7 +23397,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25392719</x:v>
+        <x:v>11885403</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23634,7 +23460,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28998566</x:v>
+        <x:v>8129332</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23697,7 +23523,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12888879</x:v>
+        <x:v>25968082</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23753,16 +23579,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c>
-        <x:v>21138.9</x:v>
-      </x:c>
-      <x:c>
-        <x:v>256.25</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>20882.65</x:v>
+        <x:v>21152.88</x:v>
+      </x:c>
+      <x:c>
+        <x:v>259.39</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>20893.49</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23784,7 +23610,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3237081</x:v>
+        <x:v>19967269</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23871,7 +23697,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8280966</x:v>
+        <x:v>3102258</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23958,7 +23784,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4157372</x:v>
+        <x:v>19720211</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24014,16 +23840,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c>
-        <x:v>37225.59</x:v>
-      </x:c>
-      <x:c>
-        <x:v>500.75</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>36724.84</x:v>
+        <x:v>37245.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>505.17</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>36740.03</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24045,7 +23871,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13778696</x:v>
+        <x:v>15949445</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24101,16 +23927,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c>
-        <x:v>37451.53</x:v>
-      </x:c>
-      <x:c>
-        <x:v>551.59</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>36899.94</x:v>
+        <x:v>37472.87</x:v>
+      </x:c>
+      <x:c>
+        <x:v>556.39</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>36916.48</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24132,7 +23958,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3291460</x:v>
+        <x:v>19141549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24219,7 +24045,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15508805</x:v>
+        <x:v>23511630</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24275,16 +24101,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c>
-        <x:v>53053.84</x:v>
-      </x:c>
-      <x:c>
-        <x:v>687.11</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>52366.73</x:v>
+        <x:v>53080.73</x:v>
+      </x:c>
+      <x:c>
+        <x:v>693.16</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>52387.57</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24306,7 +24132,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9391980</x:v>
+        <x:v>19041140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24362,16 +24188,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c>
-        <x:v>53475.65</x:v>
-      </x:c>
-      <x:c>
-        <x:v>782.02</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>52693.63</x:v>
+        <x:v>53505.89</x:v>
+      </x:c>
+      <x:c>
+        <x:v>788.82</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>52717.07</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24393,7 +24219,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15073871</x:v>
+        <x:v>17906798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24449,16 +24275,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c>
-        <x:v>52823.46</x:v>
-      </x:c>
-      <x:c>
-        <x:v>635.27</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>52188.19</x:v>
+        <x:v>52856.66</x:v>
+      </x:c>
+      <x:c>
+        <x:v>642.74</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>52213.92</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24480,7 +24306,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9908148</x:v>
+        <x:v>8728774</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24567,7 +24393,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9595158</x:v>
+        <x:v>28221140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24654,7 +24480,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15249550</x:v>
+        <x:v>22767410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24741,7 +24567,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3970995</x:v>
+        <x:v>19900547</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24828,7 +24654,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12781222</x:v>
+        <x:v>26075183</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24915,7 +24741,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10208333</x:v>
+        <x:v>28547247</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25002,7 +24828,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16252880</x:v>
+        <x:v>21799081</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25089,7 +24915,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9120982</x:v>
+        <x:v>15116855</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25176,7 +25002,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16788982</x:v>
+        <x:v>22277665</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25263,7 +25089,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3431520</x:v>
+        <x:v>19407547</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25350,7 +25176,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16615264</x:v>
+        <x:v>22331500</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25437,7 +25263,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2667669</x:v>
+        <x:v>20260889</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25524,7 +25350,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1697055</x:v>
+        <x:v>21752242</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25603,7 +25429,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>10749034</x:v>
+        <x:v>27266075</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25682,7 +25508,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>14796002</x:v>
+        <x:v>24115994</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25761,7 +25587,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>13533720</x:v>
+        <x:v>24551329</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25840,7 +25666,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>9513713</x:v>
+        <x:v>28403205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25919,7 +25745,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>16750424</x:v>
+        <x:v>22204798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25998,7 +25824,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>11316896</x:v>
+        <x:v>26724063</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26061,7 +25887,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12530818</x:v>
+        <x:v>27386727</x:v>
       </x:c>
     </x:row>
     <x:row/>

--- a/posicoes/BTG.xlsx
+++ b/posicoes/BTG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R24d9f966370f4155"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R4ea596fbeb20425a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -247,7 +247,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24873315</x:v>
+        <x:v>29619605</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +339,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16657486</x:v>
+        <x:v>21886790</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -431,7 +431,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18916268</x:v>
+        <x:v>19771901</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -523,7 +523,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16697387</x:v>
+        <x:v>21961312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -615,7 +615,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21005588</x:v>
+        <x:v>17712179</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -707,7 +707,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16098239</x:v>
+        <x:v>22600056</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -799,7 +799,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3204601</x:v>
+        <x:v>22930375</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -891,7 +891,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29329233</x:v>
+        <x:v>24942629</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -983,7 +983,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24853517</x:v>
+        <x:v>29636246</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1075,7 +1075,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30851684</x:v>
+        <x:v>24517226</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1167,7 +1167,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23825467</x:v>
+        <x:v>30696133</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1259,7 +1259,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16981538</x:v>
+        <x:v>21542134</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1351,7 +1351,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27066891</x:v>
+        <x:v>28368873</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1443,7 +1443,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21001200</x:v>
+        <x:v>17713322</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1535,7 +1535,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26261238</x:v>
+        <x:v>29133453</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1627,7 +1627,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19796208</x:v>
+        <x:v>18919507</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +1719,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22837472</x:v>
+        <x:v>10810629</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1811,7 +1811,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25632985</x:v>
+        <x:v>28973740</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1903,7 +1903,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24363778</x:v>
+        <x:v>31030002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1995,7 +1995,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23367284</x:v>
+        <x:v>13250934</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2073,7 +2073,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18126659</x:v>
+        <x:v>21376735</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2151,7 +2151,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16599864</x:v>
+        <x:v>23104471</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2229,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26557054</x:v>
+        <x:v>27985780</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2307,7 +2307,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25348539</x:v>
+        <x:v>30118169</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2387,7 +2387,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26512934</x:v>
+        <x:v>27913256</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2467,7 +2467,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16496928</x:v>
+        <x:v>23084704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2547,7 +2547,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21858760</x:v>
+        <x:v>15809597</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2627,7 +2627,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26769761</x:v>
+        <x:v>27673751</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2707,7 +2707,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23390616</x:v>
+        <x:v>12827483</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2787,7 +2787,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20501451</x:v>
+        <x:v>19066274</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2867,7 +2867,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22853319</x:v>
+        <x:v>10759638</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2947,7 +2947,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16347298</x:v>
+        <x:v>23365228</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3031,7 +3031,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18809349</x:v>
+        <x:v>19884273</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3099,7 +3099,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28283202</x:v>
+        <x:v>27206240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3191,7 +3191,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24116579</x:v>
+        <x:v>31229784</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3283,7 +3283,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17494514</x:v>
+        <x:v>22029264</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3375,7 +3375,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16835890</x:v>
+        <x:v>21831928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3467,7 +3467,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27691056</x:v>
+        <x:v>26722847</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3559,7 +3559,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17967625</x:v>
+        <x:v>20700530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3637,7 +3637,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16034172</x:v>
+        <x:v>22536010</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3715,7 +3715,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24296901</x:v>
+        <x:v>31069352</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3793,7 +3793,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28304942</x:v>
+        <x:v>27184386</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3871,7 +3871,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25128620</x:v>
+        <x:v>30460695</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3949,7 +3949,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25323603</x:v>
+        <x:v>30148866</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4027,7 +4027,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24444692</x:v>
+        <x:v>31049319</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4105,7 +4105,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18393519</x:v>
+        <x:v>21120968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4183,7 +4183,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25872178</x:v>
+        <x:v>28695244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4261,7 +4261,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19909138</x:v>
+        <x:v>18696932</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4339,7 +4339,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29046205</x:v>
+        <x:v>26371242</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4417,7 +4417,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24464602</x:v>
+        <x:v>31037743</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4495,7 +4495,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16182142</x:v>
+        <x:v>23416842</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4573,7 +4573,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17196260</x:v>
+        <x:v>22470305</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4651,7 +4651,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29868028</x:v>
+        <x:v>25565480</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4729,7 +4729,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31102328</x:v>
+        <x:v>24275396</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4807,7 +4807,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29074255</x:v>
+        <x:v>26203060</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4885,7 +4885,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26735006</x:v>
+        <x:v>27841506</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4955,7 +4955,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19994981</x:v>
+        <x:v>18612933</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5025,7 +5025,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23078298</x:v>
+        <x:v>14056639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5095,7 +5095,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28310998</x:v>
+        <x:v>27174645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5165,7 +5165,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20090443</x:v>
+        <x:v>18633977</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5245,7 +5245,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28149799</x:v>
+        <x:v>27241481</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5325,7 +5325,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22098445</x:v>
+        <x:v>17586680</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5409,7 +5409,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>17274601</x:v>
+        <x:v>22257740</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5493,7 +5493,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>28853876</x:v>
+        <x:v>26458510</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5577,7 +5577,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>29410125</x:v>
+        <x:v>24982419</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5661,7 +5661,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>29512232</x:v>
+        <x:v>24903340</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5729,7 +5729,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29176689</x:v>
+        <x:v>25756967</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5821,7 +5821,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19638728</x:v>
+        <x:v>18858076</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5913,7 +5913,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18599116</x:v>
+        <x:v>19916432</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6005,7 +6005,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28632344</x:v>
+        <x:v>25351686</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6097,7 +6097,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28039943</x:v>
+        <x:v>26818639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6189,7 +6189,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28745006</x:v>
+        <x:v>25260488</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6281,7 +6281,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29784889</x:v>
+        <x:v>25181350</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6359,7 +6359,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17464767</x:v>
+        <x:v>22169512</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6437,7 +6437,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30346921</x:v>
+        <x:v>23793810</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6515,7 +6515,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28351209</x:v>
+        <x:v>25604766</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6593,7 +6593,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29828799</x:v>
+        <x:v>25132943</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6671,7 +6671,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21127603</x:v>
+        <x:v>18335579</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6749,7 +6749,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24846654</x:v>
+        <x:v>29108621</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6827,7 +6827,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24822949</x:v>
+        <x:v>29144157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6905,7 +6905,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27819093</x:v>
+        <x:v>27026751</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6983,7 +6983,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26051038</x:v>
+        <x:v>28775554</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7061,7 +7061,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22186242</x:v>
+        <x:v>17430439</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7139,7 +7139,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26151926</x:v>
+        <x:v>28683192</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7217,7 +7217,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17903728</x:v>
+        <x:v>20761450</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7295,7 +7295,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22504916</x:v>
+        <x:v>11627590</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7373,7 +7373,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17024511</x:v>
+        <x:v>21542457</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7451,7 +7451,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16833957</x:v>
+        <x:v>21832851</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7529,7 +7529,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30842664</x:v>
+        <x:v>24273923</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7607,7 +7607,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17125893</x:v>
+        <x:v>22373496</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7685,7 +7685,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21394334</x:v>
+        <x:v>18072949</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7763,7 +7763,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28812936</x:v>
+        <x:v>25312506</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7841,7 +7841,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17492650</x:v>
+        <x:v>22022353</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7919,7 +7919,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27765979</x:v>
+        <x:v>26286066</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7997,7 +7997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17637688</x:v>
+        <x:v>20955849</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8075,7 +8075,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27420196</x:v>
+        <x:v>26473901</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8153,7 +8153,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19775773</x:v>
+        <x:v>18717699</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8231,7 +8231,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17961657</x:v>
+        <x:v>20574133</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8309,7 +8309,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28490393</x:v>
+        <x:v>25475965</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8387,7 +8387,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16184221</x:v>
+        <x:v>23272181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8465,7 +8465,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20887281</x:v>
+        <x:v>17606269</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8535,7 +8535,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24756897</x:v>
+        <x:v>29056333</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8605,7 +8605,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30539486</x:v>
+        <x:v>23496935</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8675,7 +8675,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26675773</x:v>
+        <x:v>27328249</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8745,7 +8745,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16339253</x:v>
+        <x:v>23241163</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8815,7 +8815,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23582034</x:v>
+        <x:v>30299430</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8885,7 +8885,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19636293</x:v>
+        <x:v>18857439</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8955,7 +8955,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27916783</x:v>
+        <x:v>26923230</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9035,7 +9035,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16047715</x:v>
+        <x:v>22477365</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9115,7 +9115,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28703620</x:v>
+        <x:v>25297272</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9195,7 +9195,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16247844</x:v>
+        <x:v>23323993</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9275,7 +9275,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20149606</x:v>
+        <x:v>19313624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9355,7 +9355,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20222816</x:v>
+        <x:v>19366586</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9435,7 +9435,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25320549</x:v>
+        <x:v>29596017</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9515,7 +9515,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22379573</x:v>
+        <x:v>17221993</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9595,7 +9595,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21862505</x:v>
+        <x:v>14171709</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9675,7 +9675,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29654004</x:v>
+        <x:v>24375458</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9759,7 +9759,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>21250997</x:v>
+        <x:v>18222812</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9843,7 +9843,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>17908518</x:v>
+        <x:v>20759190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9923,7 +9923,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29614044</x:v>
+        <x:v>24543398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10003,7 +10003,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25050197</x:v>
+        <x:v>29736959</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10071,7 +10071,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11512698</x:v>
+        <x:v>12977328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10163,7 +10163,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7208913</x:v>
+        <x:v>107241</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10255,7 +10255,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10326890</x:v>
+        <x:v>14598094</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10347,7 +10347,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1343958</x:v>
+        <x:v>6972411</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10425,7 +10425,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3605002</x:v>
+        <x:v>4695670</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10503,7 +10503,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7957736</x:v>
+        <x:v>16192843</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10581,7 +10581,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8174868</x:v>
+        <x:v>15936162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10659,7 +10659,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>78160</x:v>
+        <x:v>7248996</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10737,7 +10737,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8022728</x:v>
+        <x:v>15959850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10815,7 +10815,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>161304</x:v>
+        <x:v>7209030</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10893,7 +10893,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9238194</x:v>
+        <x:v>15736732</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10971,7 +10971,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13783998</x:v>
+        <x:v>9400979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11049,7 +11049,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6158330</x:v>
+        <x:v>1052037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11127,7 +11127,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5747999</x:v>
+        <x:v>1465202</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11205,7 +11205,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13483136</x:v>
+        <x:v>10583389</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11283,7 +11283,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7773326</x:v>
+        <x:v>16256233</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11361,7 +11361,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14377904</x:v>
+        <x:v>9799885</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11439,7 +11439,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8067058</x:v>
+        <x:v>16039485</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11517,7 +11517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6131094</x:v>
+        <x:v>1079309</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11595,7 +11595,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2825308</x:v>
+        <x:v>4460667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11673,7 +11673,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>829686</x:v>
+        <x:v>6379016</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11743,7 +11743,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10230110</x:v>
+        <x:v>14745907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11813,7 +11813,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8763291</x:v>
+        <x:v>15207649</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11883,7 +11883,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2150394</x:v>
+        <x:v>5025760</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11953,7 +11953,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10572544</x:v>
+        <x:v>14320296</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12033,7 +12033,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3474491</x:v>
+        <x:v>4825767</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12113,7 +12113,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15066498</x:v>
+        <x:v>7994348</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12193,7 +12193,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>977200</x:v>
+        <x:v>6352788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12261,7 +12261,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28828867</x:v>
+        <x:v>26480178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12341,7 +12341,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18513492</x:v>
+        <x:v>20992519</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12409,7 +12409,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29043328</x:v>
+        <x:v>26377559</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12501,7 +12501,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27717783</x:v>
+        <x:v>26824681</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12593,7 +12593,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27944057</x:v>
+        <x:v>27485216</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12685,7 +12685,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28483513</x:v>
+        <x:v>25850842</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12777,7 +12777,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27413679</x:v>
+        <x:v>27016716</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12869,7 +12869,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24229546</x:v>
+        <x:v>31165967</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12961,7 +12961,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24148368</x:v>
+        <x:v>31154030</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13053,7 +13053,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24266569</x:v>
+        <x:v>31087861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13145,7 +13145,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17666111</x:v>
+        <x:v>20953944</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13237,7 +13237,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16863128</x:v>
+        <x:v>21691755</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13329,7 +13329,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22492278</x:v>
+        <x:v>17194298</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13421,7 +13421,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22930334</x:v>
+        <x:v>1275464</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13513,7 +13513,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24174089</x:v>
+        <x:v>31141321</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13605,7 +13605,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19768737</x:v>
+        <x:v>18828742</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13697,7 +13697,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30780651</x:v>
+        <x:v>24468204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13789,7 +13789,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20714547</x:v>
+        <x:v>17875073</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13881,7 +13881,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19269398</x:v>
+        <x:v>20312310</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13973,7 +13973,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22937839</x:v>
+        <x:v>823822</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14065,7 +14065,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29633628</x:v>
+        <x:v>24772230</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14157,7 +14157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27171806</x:v>
+        <x:v>28278138</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14249,7 +14249,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20815504</x:v>
+        <x:v>17908404</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14341,7 +14341,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22411621</x:v>
+        <x:v>17158852</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14433,7 +14433,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4956104</x:v>
+        <x:v>23000924</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14525,7 +14525,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19159935</x:v>
+        <x:v>20406025</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14617,7 +14617,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20445722</x:v>
+        <x:v>19125663</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14709,7 +14709,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23932089</x:v>
+        <x:v>30602068</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14787,7 +14787,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22974927</x:v>
+        <x:v>5930974</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14865,7 +14865,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22578659</x:v>
+        <x:v>11276438</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14943,7 +14943,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25200569</x:v>
+        <x:v>30269641</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15021,7 +15021,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28658786</x:v>
+        <x:v>25782945</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15099,7 +15099,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27765466</x:v>
+        <x:v>26778569</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15177,7 +15177,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18245135</x:v>
+        <x:v>21273156</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15255,7 +15255,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28064001</x:v>
+        <x:v>27348990</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15333,7 +15333,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21903992</x:v>
+        <x:v>14726695</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15411,7 +15411,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27848596</x:v>
+        <x:v>26674207</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15489,7 +15489,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16726307</x:v>
+        <x:v>21936998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15567,7 +15567,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30265921</x:v>
+        <x:v>25140262</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15645,7 +15645,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30476620</x:v>
+        <x:v>23805206</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15723,7 +15723,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24215514</x:v>
+        <x:v>31173631</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15801,7 +15801,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26652030</x:v>
+        <x:v>27793372</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15879,7 +15879,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25417375</x:v>
+        <x:v>30172821</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15957,7 +15957,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27470939</x:v>
+        <x:v>27072692</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16035,7 +16035,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20556692</x:v>
+        <x:v>19137099</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16113,7 +16113,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17438856</x:v>
+        <x:v>22224200</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16191,7 +16191,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30485884</x:v>
+        <x:v>23908850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16269,7 +16269,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23611361</x:v>
+        <x:v>30985356</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16347,7 +16347,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28698438</x:v>
+        <x:v>25625120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16425,7 +16425,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26664328</x:v>
+        <x:v>27781413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16503,7 +16503,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26013885</x:v>
+        <x:v>29398206</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16581,7 +16581,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19870137</x:v>
+        <x:v>18732158</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16659,7 +16659,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29750812</x:v>
+        <x:v>24651798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16737,7 +16737,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28210807</x:v>
+        <x:v>27295873</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16815,7 +16815,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18618464</x:v>
+        <x:v>19952078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16893,7 +16893,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19020210</x:v>
+        <x:v>19566200</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16971,7 +16971,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25917968</x:v>
+        <x:v>29507198</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17049,7 +17049,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20483319</x:v>
+        <x:v>19085053</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17127,7 +17127,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21902590</x:v>
+        <x:v>14714914</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17205,7 +17205,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28139809</x:v>
+        <x:v>27249090</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17283,7 +17283,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21303285</x:v>
+        <x:v>18266731</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17361,7 +17361,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30656840</x:v>
+        <x:v>23734303</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17439,7 +17439,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25625173</x:v>
+        <x:v>28977011</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17517,7 +17517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21478284</x:v>
+        <x:v>18093331</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17595,7 +17595,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17691952</x:v>
+        <x:v>20921100</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17673,7 +17673,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16720580</x:v>
+        <x:v>21939288</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17751,7 +17751,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26552311</x:v>
+        <x:v>27875589</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17829,7 +17829,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17893644</x:v>
+        <x:v>20643898</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17907,7 +17907,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22653755</x:v>
+        <x:v>11006444</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17985,7 +17985,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26707861</x:v>
+        <x:v>27867648</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18055,7 +18055,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29955369</x:v>
+        <x:v>25368263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18125,7 +18125,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29146075</x:v>
+        <x:v>26252729</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18195,7 +18195,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20620377</x:v>
+        <x:v>17973327</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18265,7 +18265,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23423006</x:v>
+        <x:v>12575123</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18335,7 +18335,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22554011</x:v>
+        <x:v>11389878</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18405,7 +18405,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25975893</x:v>
+        <x:v>29569824</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18475,7 +18475,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24244611</x:v>
+        <x:v>31157046</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18545,7 +18545,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25954843</x:v>
+        <x:v>29589492</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18615,7 +18615,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22696188</x:v>
+        <x:v>10875050</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18685,7 +18685,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24810390</x:v>
+        <x:v>29804791</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18755,7 +18755,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28778480</x:v>
+        <x:v>25658872</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18825,7 +18825,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28234966</x:v>
+        <x:v>27126544</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18895,7 +18895,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19682933</x:v>
+        <x:v>19046367</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18965,7 +18965,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27330653</x:v>
+        <x:v>28129826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19035,7 +19035,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19015746</x:v>
+        <x:v>19569634</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19105,7 +19105,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30772042</x:v>
+        <x:v>23611604</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19175,7 +19175,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23484605</x:v>
+        <x:v>12919416</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19245,7 +19245,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23035074</x:v>
+        <x:v>13879578</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19315,7 +19315,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23521040</x:v>
+        <x:v>30939560</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19385,7 +19385,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19835758</x:v>
+        <x:v>18883992</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19455,7 +19455,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21834459</x:v>
+        <x:v>14595844</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19535,7 +19535,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22976543</x:v>
+        <x:v>6012390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19615,7 +19615,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24148232</x:v>
+        <x:v>31154067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19695,7 +19695,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23294303</x:v>
+        <x:v>13155752</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19775,7 +19775,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30770359</x:v>
+        <x:v>23616556</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19855,7 +19855,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17469077</x:v>
+        <x:v>22182942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19939,7 +19939,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>27602496</x:v>
+        <x:v>26961874</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20019,7 +20019,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27884310</x:v>
+        <x:v>26634488</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20103,7 +20103,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>16278782</x:v>
+        <x:v>23311309</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20183,7 +20183,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21668501</x:v>
+        <x:v>16621310</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20263,7 +20263,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22448734</x:v>
+        <x:v>17123374</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20331,7 +20331,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13420213</x:v>
+        <x:v>10272755</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20423,7 +20423,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1879609</x:v>
+        <x:v>6781616</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20515,7 +20515,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10944687</x:v>
+        <x:v>14599289</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20607,7 +20607,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10888415</x:v>
+        <x:v>14711265</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20699,7 +20699,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9619578</x:v>
+        <x:v>14878922</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20791,7 +20791,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10275570</x:v>
+        <x:v>14191469</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20883,7 +20883,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4193468</x:v>
+        <x:v>3379695</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20975,7 +20975,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15860811</x:v>
+        <x:v>8490740</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21067,7 +21067,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6453841</x:v>
+        <x:v>1266857</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21159,7 +21159,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6198916</x:v>
+        <x:v>2512219</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21251,7 +21251,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5442712</x:v>
+        <x:v>2272270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21343,7 +21343,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15495270</x:v>
+        <x:v>8061574</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21435,7 +21435,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1048551</x:v>
+        <x:v>7497392</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21527,7 +21527,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7524034</x:v>
+        <x:v>207524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21619,7 +21619,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1399408</x:v>
+        <x:v>6266252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21711,7 +21711,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7070449</x:v>
+        <x:v>1645966</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21803,7 +21803,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13448148</x:v>
+        <x:v>10115887</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21881,7 +21881,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10368137</x:v>
+        <x:v>13949097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21961,7 +21961,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4524442</x:v>
+        <x:v>3175166</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22029,7 +22029,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19346570</x:v>
+        <x:v>20344422</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22113,7 +22113,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>19006672</x:v>
+        <x:v>19581731</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22181,7 +22181,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22801628</x:v>
+        <x:v>8590007</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22265,7 +22265,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>18177545</x:v>
+        <x:v>21445042</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22333,7 +22333,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18906297</x:v>
+        <x:v>19777893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22413,7 +22413,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16141698</x:v>
+        <x:v>23458618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22493,7 +22493,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24424726</x:v>
+        <x:v>31059019</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22573,7 +22573,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25114530</x:v>
+        <x:v>30360292</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22653,7 +22653,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17254040</x:v>
+        <x:v>22281592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22733,7 +22733,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24378411</x:v>
+        <x:v>31022847</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22801,7 +22801,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23116018</x:v>
+        <x:v>13989295</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22879,7 +22879,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21252561</x:v>
+        <x:v>18438222</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22949,7 +22949,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21311609</x:v>
+        <x:v>18261511</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23029,7 +23029,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16474360</x:v>
+        <x:v>23227954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23109,7 +23109,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25674172</x:v>
+        <x:v>28804168</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23177,7 +23177,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15427618</x:v>
+        <x:v>8623968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23269,7 +23269,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>93653</x:v>
+        <x:v>7340130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23361,7 +23361,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11777399</x:v>
+        <x:v>11628701</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23441,7 +23441,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2264749</x:v>
+        <x:v>5905188</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23509,7 +23509,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26014446</x:v>
+        <x:v>28807502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23577,7 +23577,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29931160</x:v>
+        <x:v>25031767</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23645,7 +23645,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8836632</x:v>
+        <x:v>15131688</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23737,7 +23737,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14221314</x:v>
+        <x:v>9830661</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23829,7 +23829,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11314416</x:v>
+        <x:v>13067091</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23921,7 +23921,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8111402</x:v>
+        <x:v>15876619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24013,7 +24013,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9814234</x:v>
+        <x:v>14119410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24105,7 +24105,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1586276</x:v>
+        <x:v>6725257</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24197,7 +24197,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5638195</x:v>
+        <x:v>2570819</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24289,7 +24289,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1824389</x:v>
+        <x:v>5488814</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24381,7 +24381,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13637745</x:v>
+        <x:v>10547656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24473,7 +24473,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13052323</x:v>
+        <x:v>10003850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24565,7 +24565,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1331391</x:v>
+        <x:v>6857785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24657,7 +24657,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>611686</x:v>
+        <x:v>7711142</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24749,7 +24749,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4618748</x:v>
+        <x:v>3573967</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24841,7 +24841,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3067458</x:v>
+        <x:v>4235943</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24933,7 +24933,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8720424</x:v>
+        <x:v>15265749</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25025,7 +25025,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14528114</x:v>
+        <x:v>9649600</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25117,7 +25117,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14907561</x:v>
+        <x:v>8151392</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25209,7 +25209,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4971874</x:v>
+        <x:v>2346135</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25301,7 +25301,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6428638</x:v>
+        <x:v>1896016</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25393,7 +25393,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9065579</x:v>
+        <x:v>15030334</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25485,7 +25485,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1994805</x:v>
+        <x:v>5308090</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25577,7 +25577,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13059888</x:v>
+        <x:v>10000795</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25669,7 +25669,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6118302</x:v>
+        <x:v>1086890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25753,7 +25753,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>1665000</x:v>
+        <x:v>6514525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25837,7 +25837,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>7196097</x:v>
+        <x:v>123390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25921,7 +25921,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>6800121</x:v>
+        <x:v>515163</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26005,7 +26005,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>11331909</x:v>
+        <x:v>13052654</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26089,7 +26089,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>11470888</x:v>
+        <x:v>12854640</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26173,7 +26173,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>2430738</x:v>
+        <x:v>5853446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26241,7 +26241,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9131374</x:v>
+        <x:v>16448640</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26309,7 +26309,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13516619</x:v>
+        <x:v>10175658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26387,7 +26387,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13954269</x:v>
+        <x:v>10626483</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26465,7 +26465,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2555655</x:v>
+        <x:v>4976795</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26543,7 +26543,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7516885</x:v>
+        <x:v>92280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26621,7 +26621,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6294216</x:v>
+        <x:v>1426929</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26699,7 +26699,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9378127</x:v>
+        <x:v>15153756</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26777,7 +26777,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13924296</x:v>
+        <x:v>10811610</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26855,7 +26855,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15565128</x:v>
+        <x:v>7992690</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26933,7 +26933,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9364726</x:v>
+        <x:v>15164775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27011,7 +27011,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4775354</x:v>
+        <x:v>3936597</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27089,7 +27089,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9731506</x:v>
+        <x:v>15799716</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27169,7 +27169,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2151964</x:v>
+        <x:v>5384977</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27249,7 +27249,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9267341</x:v>
+        <x:v>15383454</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27329,7 +27329,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5184295</x:v>
+        <x:v>3533226</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27409,7 +27409,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8853596</x:v>
+        <x:v>16754265</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27489,7 +27489,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2629357</x:v>
+        <x:v>5027819</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27569,7 +27569,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15829501</x:v>
+        <x:v>8681586</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27649,7 +27649,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11056125</x:v>
+        <x:v>14461839</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27717,7 +27717,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30807003</x:v>
+        <x:v>24441312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27797,7 +27797,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19305572</x:v>
+        <x:v>20386290</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27877,7 +27877,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30094782</x:v>
+        <x:v>25183352</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27957,7 +27957,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16399840</x:v>
+        <x:v>23182247</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28037,7 +28037,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18802306</x:v>
+        <x:v>19886318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28117,7 +28117,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23486774</x:v>
+        <x:v>12909426</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28197,7 +28197,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18241217</x:v>
+        <x:v>21277541</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28277,7 +28277,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30899356</x:v>
+        <x:v>24348455</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28357,7 +28357,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18749987</x:v>
+        <x:v>19810124</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28425,7 +28425,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16010617</x:v>
+        <x:v>22626447</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28517,7 +28517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26803176</x:v>
+        <x:v>27208352</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28597,7 +28597,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16948055</x:v>
+        <x:v>21713789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28677,7 +28677,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21215523</x:v>
+        <x:v>18256340</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28757,7 +28757,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23795863</x:v>
+        <x:v>30067544</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28837,7 +28837,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22071312</x:v>
+        <x:v>17531221</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28917,7 +28917,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28122946</x:v>
+        <x:v>26861296</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28997,7 +28997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23256360</x:v>
+        <x:v>13238230</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29077,7 +29077,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22993448</x:v>
+        <x:v>14015485</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29157,7 +29157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23309746</x:v>
+        <x:v>12576601</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29237,7 +29237,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23659604</x:v>
+        <x:v>30096158</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29317,7 +29317,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27584646</x:v>
+        <x:v>26344569</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29397,7 +29397,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27246317</x:v>
+        <x:v>27674652</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29477,7 +29477,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25401442</x:v>
+        <x:v>28456924</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29557,7 +29557,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27553180</x:v>
+        <x:v>26373550</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29637,7 +29637,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29411900</x:v>
+        <x:v>24722438</x:v>
       </x:c>
     </x:row>
     <x:row/>

--- a/posicoes/BTG.xlsx
+++ b/posicoes/BTG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Re094188eb5e0431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R4d180cffa2a04240"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -247,7 +247,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26514704</x:v>
+        <x:v>33197933</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -291,16 +291,16 @@
         <x:v>229.0788549</x:v>
       </x:c>
       <x:c>
-        <x:v>73274.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>267.96</x:v>
-      </x:c>
-      <x:c>
-        <x:v>87.97</x:v>
-      </x:c>
-      <x:c>
-        <x:v>72918.47</x:v>
+        <x:v>73315.76</x:v>
+      </x:c>
+      <x:c>
+        <x:v>276.12</x:v>
+      </x:c>
+      <x:c>
+        <x:v>93.04</x:v>
+      </x:c>
+      <x:c>
+        <x:v>72946.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -327,7 +327,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22242526</x:v>
+        <x:v>20550626</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -407,7 +407,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18060058</x:v>
+        <x:v>24875816</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -487,7 +487,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18322183</x:v>
+        <x:v>24615040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -567,7 +567,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21949173</x:v>
+        <x:v>19684384</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -647,7 +647,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17706949</x:v>
+        <x:v>24123761</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -727,7 +727,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19295543</x:v>
+        <x:v>21441698</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -771,16 +771,16 @@
         <x:v>4172.9117</x:v>
       </x:c>
       <x:c>
-        <x:v>38242.48</x:v>
-      </x:c>
-      <x:c>
-        <x:v>268.35</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>37974.13</x:v>
+        <x:v>38263.46</x:v>
+      </x:c>
+      <x:c>
+        <x:v>272.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>37990.66</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -807,7 +807,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23036868</x:v>
+        <x:v>20829057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -887,7 +887,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22164132</x:v>
+        <x:v>20612788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -943,16 +943,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c>
-        <x:v>187184.85</x:v>
-      </x:c>
-      <x:c>
-        <x:v>7077.72</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>180107.13</x:v>
+        <x:v>187277.49</x:v>
+      </x:c>
+      <x:c>
+        <x:v>7091.62</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>180185.87</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -979,7 +979,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26397030</x:v>
+        <x:v>25672152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26234129</x:v>
+        <x:v>32528174</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1163,7 +1163,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33377259</x:v>
+        <x:v>27310216</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1255,7 +1255,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21292405</x:v>
+        <x:v>19383583</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1347,7 +1347,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23230819</x:v>
+        <x:v>17424071</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1439,7 +1439,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22671388</x:v>
+        <x:v>21138053</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1531,7 +1531,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27134417</x:v>
+        <x:v>33647870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1623,7 +1623,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31961469</x:v>
+        <x:v>25590080</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1715,7 +1715,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26146044</x:v>
+        <x:v>32554353</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1807,7 +1807,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28343752</x:v>
+        <x:v>30274095</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +1899,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19993069</x:v>
+        <x:v>21767314</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1991,7 +1991,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18329711</x:v>
+        <x:v>24607877</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2083,7 +2083,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19461752</x:v>
+        <x:v>21215625</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2175,7 +2175,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29537920</x:v>
+        <x:v>28024630</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2267,7 +2267,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21410665</x:v>
+        <x:v>19255476</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2359,7 +2359,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12449158</x:v>
+        <x:v>24224116</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2451,7 +2451,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24185057</x:v>
+        <x:v>17478997</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2543,7 +2543,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23803655</x:v>
+        <x:v>17887246</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2635,7 +2635,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22581568</x:v>
+        <x:v>20088449</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2713,7 +2713,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18745826</x:v>
+        <x:v>25170026</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2757,14 +2757,14 @@
         <x:v>1155</x:v>
       </x:c>
       <x:c>
-        <x:v>113548.05</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>113548.05</x:v>
+        <x:v>113467.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>113467.2</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2791,7 +2791,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21253473</x:v>
+        <x:v>27813756</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2835,14 +2835,14 @@
         <x:v>694</x:v>
       </x:c>
       <x:c>
-        <x:v>70267.5</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>70267.5</x:v>
+        <x:v>70274.44</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>70274.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2869,7 +2869,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31971718</x:v>
+        <x:v>21845271</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2913,14 +2913,14 @@
         <x:v>565</x:v>
       </x:c>
       <x:c>
-        <x:v>54014</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>54014</x:v>
+        <x:v>53940.55</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>53940.55</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2947,7 +2947,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27522314</x:v>
+        <x:v>32634178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3017,7 +3017,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18137365</x:v>
+        <x:v>24693663</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3087,7 +3087,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18321392</x:v>
+        <x:v>24615796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3157,7 +3157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21551315</x:v>
+        <x:v>19121152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3227,7 +3227,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21134029</x:v>
+        <x:v>19511503</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3315,7 +3315,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20464341</x:v>
+        <x:v>22356885</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3383,7 +3383,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30295326</x:v>
+        <x:v>28279992</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3463,7 +3463,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20879492</x:v>
+        <x:v>23044094</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3507,16 +3507,16 @@
         <x:v>154.5199</x:v>
       </x:c>
       <x:c>
-        <x:v>1416.09</x:v>
-      </x:c>
-      <x:c>
-        <x:v>14.09</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1402</x:v>
+        <x:v>1416.87</x:v>
+      </x:c>
+      <x:c>
+        <x:v>14.25</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1402.62</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3543,7 +3543,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19193037</x:v>
+        <x:v>21471518</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3591,12 +3591,12 @@
         <x:v>78906.75587022</x:v>
       </x:c>
       <x:c>
-        <x:v>126348.12</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>126348.12</x:v>
+        <x:v>126417.26</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>126417.26</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3627,7 +3627,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>31778110</x:v>
+        <x:v>21717270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3675,12 +3675,12 @@
         <x:v>110039.977259</x:v>
       </x:c>
       <x:c>
-        <x:v>144370.11</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>144370.11</x:v>
+        <x:v>144096.5</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>144096.5</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3711,7 +3711,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>19901725</x:v>
+        <x:v>32704738</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3759,12 +3759,12 @@
         <x:v>78330.53174071</x:v>
       </x:c>
       <x:c>
-        <x:v>125425.45</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>125425.45</x:v>
+        <x:v>125494.08</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>125494.08</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3795,7 +3795,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>31198764</x:v>
+        <x:v>19719972</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3879,7 +3879,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>32225196</x:v>
+        <x:v>26394305</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21875837</x:v>
+        <x:v>19870658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4063,7 +4063,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2546418</x:v>
+        <x:v>23751302</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4155,7 +4155,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18054987</x:v>
+        <x:v>24870673</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4247,7 +4247,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31259083</x:v>
+        <x:v>29377128</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4339,7 +4339,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30632870</x:v>
+        <x:v>28997824</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4417,7 +4417,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23413989</x:v>
+        <x:v>13030573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4495,7 +4495,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28462478</x:v>
+        <x:v>31323542</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4573,7 +4573,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29589156</x:v>
+        <x:v>27945922</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4651,7 +4651,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31347289</x:v>
+        <x:v>29349780</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4729,7 +4729,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28269557</x:v>
+        <x:v>30466345</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4807,7 +4807,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1616785</x:v>
+        <x:v>23876965</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4885,7 +4885,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5605993</x:v>
+        <x:v>23359610</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4963,7 +4963,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18602743</x:v>
+        <x:v>25277066</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5041,7 +5041,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21270272</x:v>
+        <x:v>19377349</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5119,7 +5119,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19227140</x:v>
+        <x:v>21505452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5197,7 +5197,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30871565</x:v>
+        <x:v>28841715</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5275,7 +5275,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3577902</x:v>
+        <x:v>23620976</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5353,7 +5353,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18937537</x:v>
+        <x:v>24947702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5431,7 +5431,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18106408</x:v>
+        <x:v>24791396</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5509,7 +5509,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20832356</x:v>
+        <x:v>23013618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5587,7 +5587,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23532585</x:v>
+        <x:v>6873134</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5665,7 +5665,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32478474</x:v>
+        <x:v>26147920</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5743,7 +5743,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20774969</x:v>
+        <x:v>23073623</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5813,7 +5813,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2875229</x:v>
+        <x:v>23632059</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5883,7 +5883,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27185106</x:v>
+        <x:v>33592517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5953,7 +5953,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18494707</x:v>
+        <x:v>25448667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6023,7 +6023,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18804068</x:v>
+        <x:v>25079034</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6093,7 +6093,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22044936</x:v>
+        <x:v>19648753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6163,7 +6163,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30898212</x:v>
+        <x:v>28755762</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6233,7 +6233,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28391396</x:v>
+        <x:v>30338508</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6303,7 +6303,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25425150</x:v>
+        <x:v>32241609</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6373,7 +6373,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19412932</x:v>
+        <x:v>21304358</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6443,7 +6443,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28935237</x:v>
+        <x:v>31816335</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6513,7 +6513,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22459576</x:v>
+        <x:v>20213216</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6581,7 +6581,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32882654</x:v>
+        <x:v>26785802</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6661,7 +6661,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20964273</x:v>
+        <x:v>22798154</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6705,16 +6705,16 @@
         <x:v>10784.950882</x:v>
       </x:c>
       <x:c>
-        <x:v>20371.79</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>20371.79</x:v>
+        <x:v>20367.45</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>20367.45</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -6741,7 +6741,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27466177</x:v>
+        <x:v>33077169</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6821,7 +6821,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24435678</x:v>
+        <x:v>18376540</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6865,16 +6865,16 @@
         <x:v>10935.210624</x:v>
       </x:c>
       <x:c>
-        <x:v>22484.47</x:v>
-      </x:c>
-      <x:c>
-        <x:v>130.94</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>22353.53</x:v>
+        <x:v>22532.53</x:v>
+      </x:c>
+      <x:c>
+        <x:v>139.35</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>22393.18</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -6901,7 +6901,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29547985</x:v>
+        <x:v>31094034</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6981,7 +6981,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26772525</x:v>
+        <x:v>32783507</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7025,16 +7025,16 @@
         <x:v>24570.4025</x:v>
       </x:c>
       <x:c>
-        <x:v>44769.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>355.51</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>44414.19</x:v>
+        <x:v>44731.62</x:v>
+      </x:c>
+      <x:c>
+        <x:v>347.9</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>44383.72</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7061,7 +7061,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30091250</x:v>
+        <x:v>27425294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7105,16 +7105,16 @@
         <x:v>33773.50649</x:v>
       </x:c>
       <x:c>
-        <x:v>73515.45</x:v>
-      </x:c>
-      <x:c>
-        <x:v>558.21</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>72957.24</x:v>
+        <x:v>73550.01</x:v>
+      </x:c>
+      <x:c>
+        <x:v>564.26</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>72985.75</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7141,7 +7141,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18033694</x:v>
+        <x:v>24697503</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7221,7 +7221,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1652142</x:v>
+        <x:v>23535890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7301,7 +7301,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24716590</x:v>
+        <x:v>18125679</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7345,16 +7345,16 @@
         <x:v>139.8694019</x:v>
       </x:c>
       <x:c>
-        <x:v>3168.68</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>3168.68</x:v>
+        <x:v>3165.64</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>3165.64</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7381,7 +7381,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30826138</x:v>
+        <x:v>28833534</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7425,16 +7425,16 @@
         <x:v>6960.5181</x:v>
       </x:c>
       <x:c>
-        <x:v>63789.39</x:v>
-      </x:c>
-      <x:c>
-        <x:v>465.86</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>63323.53</x:v>
+        <x:v>63824.37</x:v>
+      </x:c>
+      <x:c>
+        <x:v>472.68</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>63351.69</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7461,7 +7461,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32408906</x:v>
+        <x:v>26151079</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7509,12 +7509,12 @@
         <x:v>10136.14741604</x:v>
       </x:c>
       <x:c>
-        <x:v>16230.34</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>16230.34</x:v>
+        <x:v>16239.22</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>16239.22</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7545,7 +7545,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>24976294</x:v>
+        <x:v>32200380</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7593,12 +7593,12 @@
         <x:v>100882.08039782</x:v>
       </x:c>
       <x:c>
-        <x:v>161535.74</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>161535.74</x:v>
+        <x:v>161624.13</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>161624.13</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7629,7 +7629,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>30856518</x:v>
+        <x:v>32417493</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7685,16 +7685,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c>
-        <x:v>9528.79</x:v>
-      </x:c>
-      <x:c>
-        <x:v>118.97</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>9409.82</x:v>
+        <x:v>9533.83</x:v>
+      </x:c>
+      <x:c>
+        <x:v>120.11</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>9413.72</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7721,7 +7721,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20817932</x:v>
+        <x:v>28475832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7813,7 +7813,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26088564</x:v>
+        <x:v>32384930</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7905,7 +7905,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33387985</x:v>
+        <x:v>27264944</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7997,7 +7997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29511113</x:v>
+        <x:v>31173291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8089,7 +8089,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21613394</x:v>
+        <x:v>19053621</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8181,7 +8181,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22086833</x:v>
+        <x:v>19768566</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8259,7 +8259,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24897870</x:v>
+        <x:v>18983434</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8337,7 +8337,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30553585</x:v>
+        <x:v>28016442</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8415,7 +8415,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22753230</x:v>
+        <x:v>20135800</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8493,7 +8493,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30821079</x:v>
+        <x:v>28811434</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8571,7 +8571,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33576883</x:v>
+        <x:v>27073529</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8649,7 +8649,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25552088</x:v>
+        <x:v>31828151</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8727,7 +8727,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17893631</x:v>
+        <x:v>23789050</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8805,7 +8805,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22568911</x:v>
+        <x:v>20228219</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8883,7 +8883,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31629631</x:v>
+        <x:v>29055511</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8961,7 +8961,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27252502</x:v>
+        <x:v>33393485</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9039,7 +9039,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20156751</x:v>
+        <x:v>22519781</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9117,7 +9117,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17867351</x:v>
+        <x:v>23748280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9195,7 +9195,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27108419</x:v>
+        <x:v>33515315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9273,7 +9273,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25842633</x:v>
+        <x:v>31596078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9351,7 +9351,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33317061</x:v>
+        <x:v>26282148</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9429,7 +9429,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17814116</x:v>
+        <x:v>23841934</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9507,7 +9507,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17725666</x:v>
+        <x:v>23868080</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9585,7 +9585,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19908298</x:v>
+        <x:v>21746807</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9663,7 +9663,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24123179</x:v>
+        <x:v>17659166</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9741,7 +9741,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18998587</x:v>
+        <x:v>24736253</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9819,7 +9819,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27699275</x:v>
+        <x:v>29800268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9897,7 +9897,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19725814</x:v>
+        <x:v>21944710</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9975,7 +9975,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19396442</x:v>
+        <x:v>21233239</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10053,7 +10053,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28317911</x:v>
+        <x:v>30251775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10131,7 +10131,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4290554</x:v>
+        <x:v>23339929</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10209,7 +10209,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18086115</x:v>
+        <x:v>24615690</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10287,7 +10287,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26518154</x:v>
+        <x:v>33073888</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10365,7 +10365,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32457208</x:v>
+        <x:v>26199338</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10443,7 +10443,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28504201</x:v>
+        <x:v>30066892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10513,7 +10513,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30935117</x:v>
+        <x:v>28659001</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10583,7 +10583,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18018340</x:v>
+        <x:v>24682969</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10653,7 +10653,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28906343</x:v>
+        <x:v>30717262</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10723,7 +10723,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20717991</x:v>
+        <x:v>23071436</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10793,7 +10793,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26814429</x:v>
+        <x:v>32709016</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10863,7 +10863,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26527032</x:v>
+        <x:v>33067261</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10933,7 +10933,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26812906</x:v>
+        <x:v>32706541</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11003,7 +11003,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2341785</x:v>
+        <x:v>23505349</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11073,7 +11073,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30493673</x:v>
+        <x:v>28099798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11143,7 +11143,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27706987</x:v>
+        <x:v>29822009</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11213,7 +11213,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22522345</x:v>
+        <x:v>20294405</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11283,7 +11283,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19955008</x:v>
+        <x:v>21774769</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11353,7 +11353,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1614127</x:v>
+        <x:v>23638895</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11423,7 +11423,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27830876</x:v>
+        <x:v>29681550</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11493,7 +11493,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33158103</x:v>
+        <x:v>26529114</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11563,7 +11563,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31208874</x:v>
+        <x:v>28388969</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11633,7 +11633,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26148678</x:v>
+        <x:v>32294990</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11703,7 +11703,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29690476</x:v>
+        <x:v>27817251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11773,7 +11773,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30097219</x:v>
+        <x:v>27448196</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11841,7 +11841,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1812828</x:v>
+        <x:v>7925504</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11921,7 +11921,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15608018</x:v>
+        <x:v>8712019</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12001,7 +12001,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17398539</x:v>
+        <x:v>10097475</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12045,16 +12045,16 @@
         <x:v>23353.3023</x:v>
       </x:c>
       <x:c>
-        <x:v>214020.38</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1959.35</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>212061.03</x:v>
+        <x:v>214137.79</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1979.9</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>212157.89</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12081,7 +12081,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14677656</x:v>
+        <x:v>11683019</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12173,7 +12173,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15909454</x:v>
+        <x:v>8345051</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12265,7 +12265,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12094353</x:v>
+        <x:v>13276543</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12357,7 +12357,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7849999</x:v>
+        <x:v>357790</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12401,14 +12401,14 @@
         <x:v>455</x:v>
       </x:c>
       <x:c>
-        <x:v>24515.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>24515.4</x:v>
+        <x:v>24438.05</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>24438.05</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12435,7 +12435,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13086186</x:v>
+        <x:v>3892097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12513,7 +12513,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13331537</x:v>
+        <x:v>14270848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12591,7 +12591,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9726206</x:v>
+        <x:v>15641740</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12635,14 +12635,14 @@
         <x:v>851</x:v>
       </x:c>
       <x:c>
-        <x:v>25759.77</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>25759.77</x:v>
+        <x:v>25640.63</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>25640.63</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12669,7 +12669,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>109545</x:v>
+        <x:v>2023627</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12713,14 +12713,14 @@
         <x:v>710</x:v>
       </x:c>
       <x:c>
-        <x:v>27746.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>27746.8</x:v>
+        <x:v>27839.1</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>27839.1</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12747,7 +12747,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>843109</x:v>
+        <x:v>13712325</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12825,7 +12825,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5123237</x:v>
+        <x:v>1912597</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12869,14 +12869,14 @@
         <x:v>793</x:v>
       </x:c>
       <x:c>
-        <x:v>35478.82</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>35478.82</x:v>
+        <x:v>35486.75</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>35486.75</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12903,7 +12903,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4896493</x:v>
+        <x:v>4115435</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12981,7 +12981,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1490337</x:v>
+        <x:v>8210656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13025,14 +13025,14 @@
         <x:v>3593</x:v>
       </x:c>
       <x:c>
-        <x:v>27558.31</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>27558.31</x:v>
+        <x:v>27594.24</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>27594.24</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -13059,7 +13059,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11001870</x:v>
+        <x:v>5936438</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13103,14 +13103,14 @@
         <x:v>1106</x:v>
       </x:c>
       <x:c>
-        <x:v>30968</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>30968</x:v>
+        <x:v>30979.06</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>30979.06</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -13137,7 +13137,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>343598</x:v>
+        <x:v>5412682</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13181,14 +13181,14 @@
         <x:v>424</x:v>
       </x:c>
       <x:c>
-        <x:v>32368.16</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>32368.16</x:v>
+        <x:v>32355.44</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>32355.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -13215,7 +13215,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4167359</x:v>
+        <x:v>11023272</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13259,14 +13259,14 @@
         <x:v>233</x:v>
       </x:c>
       <x:c>
-        <x:v>34388.47</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>34388.47</x:v>
+        <x:v>34390.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>34390.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -13293,7 +13293,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7879476</x:v>
+        <x:v>5451510</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13337,14 +13337,14 @@
         <x:v>300</x:v>
       </x:c>
       <x:c>
-        <x:v>36810</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>36810</x:v>
+        <x:v>36690</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>36690</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -13371,7 +13371,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6796972</x:v>
+        <x:v>277120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13415,14 +13415,14 @@
         <x:v>400</x:v>
       </x:c>
       <x:c>
-        <x:v>35564</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>35564</x:v>
+        <x:v>35552</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>35552</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -13449,7 +13449,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1186871</x:v>
+        <x:v>7596491</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13493,14 +13493,14 @@
         <x:v>259</x:v>
       </x:c>
       <x:c>
-        <x:v>39627</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>39627</x:v>
+        <x:v>39391.31</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>39391.31</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -13527,7 +13527,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16803336</x:v>
+        <x:v>11835314</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13605,7 +13605,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5927622</x:v>
+        <x:v>3226065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13683,7 +13683,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12139314</x:v>
+        <x:v>13196458</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13761,7 +13761,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11922606</x:v>
+        <x:v>13521748</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13831,7 +13831,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16402988</x:v>
+        <x:v>8985344</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13901,7 +13901,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8285576</x:v>
+        <x:v>981231</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13971,7 +13971,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16651159</x:v>
+        <x:v>9749174</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14041,7 +14041,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16875235</x:v>
+        <x:v>9588477</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14111,7 +14111,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9782549</x:v>
+        <x:v>15681931</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14181,7 +14181,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1066758</x:v>
+        <x:v>7545276</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14251,7 +14251,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7705230</x:v>
+        <x:v>493929</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14321,7 +14321,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5114245</x:v>
+        <x:v>1920326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14391,7 +14391,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15645227</x:v>
+        <x:v>8630077</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14461,7 +14461,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12874820</x:v>
+        <x:v>14636966</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14529,7 +14529,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33553791</x:v>
+        <x:v>27089219</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14609,7 +14609,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18792391</x:v>
+        <x:v>25084471</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14677,7 +14677,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25742827</x:v>
+        <x:v>31895111</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14757,7 +14757,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24674049</x:v>
+        <x:v>17970673</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14801,16 +14801,16 @@
         <x:v>27715.617034</x:v>
       </x:c>
       <x:c>
-        <x:v>149471.37</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1109.66</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>148361.71</x:v>
+        <x:v>149549.31</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1123.3</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>148426.01</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -14837,7 +14837,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27658984</x:v>
+        <x:v>29969600</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14917,7 +14917,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23902497</x:v>
+        <x:v>17705823</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14961,16 +14961,16 @@
         <x:v>59.67945939</x:v>
       </x:c>
       <x:c>
-        <x:v>29920.59</x:v>
-      </x:c>
-      <x:c>
-        <x:v>193.77</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>29726.82</x:v>
+        <x:v>29985.11</x:v>
+      </x:c>
+      <x:c>
+        <x:v>205.06</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>29780.05</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -14997,7 +14997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20860333</x:v>
+        <x:v>23025530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15077,7 +15077,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30412906</x:v>
+        <x:v>28267578</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15157,7 +15157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28810892</x:v>
+        <x:v>30896155</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15201,16 +15201,16 @@
         <x:v>2496.1044</x:v>
       </x:c>
       <x:c>
-        <x:v>22875.45</x:v>
-      </x:c>
-      <x:c>
-        <x:v>155.74</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>22719.71</x:v>
+        <x:v>22888</x:v>
+      </x:c>
+      <x:c>
+        <x:v>158.56</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>22729.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15237,7 +15237,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26892627</x:v>
+        <x:v>33779420</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15317,7 +15317,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20410689</x:v>
+        <x:v>22450829</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15401,7 +15401,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>30178221</x:v>
+        <x:v>28407837</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15449,12 +15449,12 @@
         <x:v>24493.92532282</x:v>
       </x:c>
       <x:c>
-        <x:v>30321.25</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>30321.25</x:v>
+        <x:v>30338.59</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>30338.59</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15485,7 +15485,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>22196177</x:v>
+        <x:v>20701807</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15577,7 +15577,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32659415</x:v>
+        <x:v>26980485</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15669,7 +15669,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28129635</x:v>
+        <x:v>30603080</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15761,7 +15761,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20259852</x:v>
+        <x:v>22564128</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15853,7 +15853,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20140965</x:v>
+        <x:v>22711789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15945,7 +15945,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18441223</x:v>
+        <x:v>24457901</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16037,7 +16037,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26796623</x:v>
+        <x:v>32942464</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16129,7 +16129,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31244343</x:v>
+        <x:v>29379253</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16221,7 +16221,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25859006</x:v>
+        <x:v>32796893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16313,7 +16313,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20150321</x:v>
+        <x:v>22705045</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16350,7 +16350,7 @@
       <x:c/>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>Marfrig</x:t>
+          <x:t>MARFRIG</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -16405,7 +16405,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27834739</x:v>
+        <x:v>29734132</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16497,7 +16497,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29381184</x:v>
+        <x:v>31344641</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16589,7 +16589,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31711516</x:v>
+        <x:v>25735384</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16681,7 +16681,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19345629</x:v>
+        <x:v>21370992</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16773,7 +16773,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32479453</x:v>
+        <x:v>26132615</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16865,7 +16865,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14904022</x:v>
+        <x:v>24285051</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16957,7 +16957,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29429119</x:v>
+        <x:v>31391702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17049,7 +17049,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32508171</x:v>
+        <x:v>26045894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17141,7 +17141,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33083362</x:v>
+        <x:v>26598857</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17233,7 +17233,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11263154</x:v>
+        <x:v>24337771</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17325,7 +17325,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20142988</x:v>
+        <x:v>22713901</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17417,7 +17417,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33358822</x:v>
+        <x:v>27291329</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17509,7 +17509,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22327309</x:v>
+        <x:v>20359776</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17601,7 +17601,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21116567</x:v>
+        <x:v>19495241</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17693,7 +17693,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33484387</x:v>
+        <x:v>27267606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17785,7 +17785,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26876530</x:v>
+        <x:v>33772107</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17863,7 +17863,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32555667</x:v>
+        <x:v>27024661</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17941,7 +17941,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24232289</x:v>
+        <x:v>18439152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18019,7 +18019,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3600524</x:v>
+        <x:v>23492785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18097,7 +18097,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25105971</x:v>
+        <x:v>18643708</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18175,7 +18175,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29314482</x:v>
+        <x:v>31407844</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18253,7 +18253,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28596254</x:v>
+        <x:v>31071017</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18331,7 +18331,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21095939</x:v>
+        <x:v>19478161</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18409,7 +18409,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24524366</x:v>
+        <x:v>18210879</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18487,7 +18487,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24986585</x:v>
+        <x:v>18787956</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18565,7 +18565,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33599433</x:v>
+        <x:v>27118678</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18643,7 +18643,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21927750</x:v>
+        <x:v>19679046</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18721,7 +18721,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10737382</x:v>
+        <x:v>24344985</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18799,7 +18799,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29629844</x:v>
+        <x:v>28003013</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18877,7 +18877,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18916552</x:v>
+        <x:v>25060715</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18955,7 +18955,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18147154</x:v>
+        <x:v>24685765</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19033,7 +19033,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21127836</x:v>
+        <x:v>19489300</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19111,7 +19111,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22269311</x:v>
+        <x:v>20456221</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19189,7 +19189,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33257996</x:v>
+        <x:v>27436683</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19267,7 +19267,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22709962</x:v>
+        <x:v>21060659</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19345,7 +19345,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25477022</x:v>
+        <x:v>32169458</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19423,7 +19423,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29379469</x:v>
+        <x:v>31344514</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19501,7 +19501,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5612125</x:v>
+        <x:v>23365999</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19579,7 +19579,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26054721</x:v>
+        <x:v>32608670</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19657,7 +19657,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17711026</x:v>
+        <x:v>24127653</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19735,7 +19735,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26667763</x:v>
+        <x:v>33073132</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19813,7 +19813,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27526846</x:v>
+        <x:v>30114827</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19891,7 +19891,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23617581</x:v>
+        <x:v>5067907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19969,7 +19969,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31683072</x:v>
+        <x:v>25844511</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20047,7 +20047,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24302357</x:v>
+        <x:v>18397705</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20125,7 +20125,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23794038</x:v>
+        <x:v>17860166</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20203,7 +20203,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23178466</x:v>
+        <x:v>17386635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20281,7 +20281,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24755229</x:v>
+        <x:v>18951978</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20359,7 +20359,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32998887</x:v>
+        <x:v>26647985</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20437,7 +20437,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29989291</x:v>
+        <x:v>28627298</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20515,7 +20515,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22299875</x:v>
+        <x:v>20489811</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20593,7 +20593,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30083521</x:v>
+        <x:v>28595046</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20671,7 +20671,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17980428</x:v>
+        <x:v>24909259</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20749,7 +20749,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33072596</x:v>
+        <x:v>26568307</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20827,7 +20827,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30963623</x:v>
+        <x:v>28690042</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20905,7 +20905,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26767019</x:v>
+        <x:v>33041424</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20983,7 +20983,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33520251</x:v>
+        <x:v>27187703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21061,7 +21061,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19077784</x:v>
+        <x:v>21620723</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21139,7 +21139,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33377679</x:v>
+        <x:v>27309571</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21209,7 +21209,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21811430</x:v>
+        <x:v>19924773</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21279,7 +21279,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26889935</x:v>
+        <x:v>33786952</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21349,7 +21349,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25165036</x:v>
+        <x:v>18591239</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21419,7 +21419,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26203873</x:v>
+        <x:v>32497034</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21489,7 +21489,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32457831</x:v>
+        <x:v>26125815</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21559,7 +21559,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22830782</x:v>
+        <x:v>21048238</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21629,7 +21629,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33268227</x:v>
+        <x:v>27448466</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21699,7 +21699,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18297896</x:v>
+        <x:v>24575235</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21769,7 +21769,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18201764</x:v>
+        <x:v>24624368</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21839,7 +21839,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32573103</x:v>
+        <x:v>27041885</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21909,7 +21909,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23932452</x:v>
+        <x:v>17754906</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21979,7 +21979,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27694847</x:v>
+        <x:v>29853368</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22049,7 +22049,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26055122</x:v>
+        <x:v>32608319</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22119,7 +22119,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19039093</x:v>
+        <x:v>21733529</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22189,7 +22189,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19343450</x:v>
+        <x:v>21352130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22259,7 +22259,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23307374</x:v>
+        <x:v>14066367</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22329,7 +22329,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23187885</x:v>
+        <x:v>17334797</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22399,7 +22399,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19359837</x:v>
+        <x:v>21368528</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22469,7 +22469,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31805033</x:v>
+        <x:v>25711283</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22539,7 +22539,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28991238</x:v>
+        <x:v>31757484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22609,7 +22609,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29435996</x:v>
+        <x:v>31399832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22679,7 +22679,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19967631</x:v>
+        <x:v>21857863</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22749,7 +22749,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31538382</x:v>
+        <x:v>25993465</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22819,7 +22819,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26214572</x:v>
+        <x:v>32507646</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22889,7 +22889,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24737869</x:v>
+        <x:v>18934666</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22959,7 +22959,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1941828</x:v>
+        <x:v>23791712</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23029,7 +23029,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19838914</x:v>
+        <x:v>21991437</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23099,7 +23099,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25839505</x:v>
+        <x:v>32908869</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23169,7 +23169,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33406292</x:v>
+        <x:v>27339329</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23239,7 +23239,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33315141</x:v>
+        <x:v>27382823</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23309,7 +23309,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27846505</x:v>
+        <x:v>29730632</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23379,7 +23379,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32351946</x:v>
+        <x:v>26266351</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23449,7 +23449,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32196826</x:v>
+        <x:v>26381840</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23517,7 +23517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6419878</x:v>
+        <x:v>4598773</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23597,7 +23597,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2298566</x:v>
+        <x:v>8663614</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23689,7 +23689,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11199505</x:v>
+        <x:v>13865603</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23781,7 +23781,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6005619</x:v>
+        <x:v>4030554</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23873,7 +23873,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5709901</x:v>
+        <x:v>3132811</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23965,7 +23965,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15373252</x:v>
+        <x:v>12918866</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24057,7 +24057,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>718863</x:v>
+        <x:v>7926924</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24113,16 +24113,16 @@
         <x:v>98</x:v>
       </x:c>
       <x:c>
-        <x:v>121892.76</x:v>
-      </x:c>
-      <x:c>
-        <x:v>4181.23</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>117711.53</x:v>
+        <x:v>121933.01</x:v>
+      </x:c>
+      <x:c>
+        <x:v>4188.27</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>117744.74</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24149,7 +24149,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6104323</x:v>
+        <x:v>450338</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24241,7 +24241,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16634245</x:v>
+        <x:v>10628950</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24333,7 +24333,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2969211</x:v>
+        <x:v>5663718</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24425,7 +24425,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4931453</x:v>
+        <x:v>2784289</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24517,7 +24517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12977596</x:v>
+        <x:v>15408937</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24609,7 +24609,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9496656</x:v>
+        <x:v>15697607</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24701,7 +24701,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2388700</x:v>
+        <x:v>8490193</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24793,7 +24793,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6882103</x:v>
+        <x:v>4236507</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24871,7 +24871,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17209922</x:v>
+        <x:v>11069156</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24941,7 +24941,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5520783</x:v>
+        <x:v>3358492</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25009,7 +25009,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21964089</x:v>
+        <x:v>19699274</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25093,7 +25093,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>32706779</x:v>
+        <x:v>26897090</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25161,7 +25161,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19511331</x:v>
+        <x:v>22216612</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25245,7 +25245,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>32408295</x:v>
+        <x:v>26209665</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25313,7 +25313,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3676791</x:v>
+        <x:v>23417792</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25357,16 +25357,16 @@
         <x:v>0.4881686</x:v>
       </x:c>
       <x:c>
-        <x:v>426.34</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1.62</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>424.72</x:v>
+        <x:v>426.57</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1.66</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>424.91</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -25393,7 +25393,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5965106</x:v>
+        <x:v>24361785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25473,7 +25473,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24921751</x:v>
+        <x:v>18855519</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25553,7 +25553,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30402402</x:v>
+        <x:v>28239452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25633,7 +25633,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33417904</x:v>
+        <x:v>27334942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25677,16 +25677,16 @@
         <x:v>8017.62959</x:v>
       </x:c>
       <x:c>
-        <x:v>27568.66</x:v>
-      </x:c>
-      <x:c>
-        <x:v>250.04</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>27318.62</x:v>
+        <x:v>27583.41</x:v>
+      </x:c>
+      <x:c>
+        <x:v>252.62</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>27330.79</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -25713,7 +25713,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33533990</x:v>
+        <x:v>27186046</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25781,7 +25781,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20583571</x:v>
+        <x:v>23279363</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25861,7 +25861,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17788979</x:v>
+        <x:v>24053437</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25941,7 +25941,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27029735</x:v>
+        <x:v>33717714</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26019,7 +26019,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30326324</x:v>
+        <x:v>28309708</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26089,7 +26089,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21307611</x:v>
+        <x:v>19266594</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26157,7 +26157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13304873</x:v>
+        <x:v>14262804</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26237,7 +26237,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5264419</x:v>
+        <x:v>2875037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26293,16 +26293,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c>
-        <x:v>4648.36</x:v>
-      </x:c>
-      <x:c>
-        <x:v>113.46</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>4534.9</x:v>
+        <x:v>4650.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>113.78</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>4536.42</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -26329,7 +26329,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17231249</x:v>
+        <x:v>14284442</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26421,7 +26421,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4336966</x:v>
+        <x:v>5856604</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26489,7 +26489,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19420617</x:v>
+        <x:v>21268934</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26557,7 +26557,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23616505</x:v>
+        <x:v>6455619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26625,7 +26625,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7841009</x:v>
+        <x:v>354168</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26673,12 +26673,12 @@
         <x:v>434890.82128813</x:v>
       </x:c>
       <x:c>
-        <x:v>538355.29</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>538355.29</x:v>
+        <x:v>538663.08</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>538663.08</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -26709,7 +26709,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>9747596</x:v>
+        <x:v>14323227</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26757,12 +26757,12 @@
         <x:v>117927.16105932</x:v>
       </x:c>
       <x:c>
-        <x:v>145983.1</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>145983.1</x:v>
+        <x:v>146066.56</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>146066.56</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -26793,7 +26793,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>3965544</x:v>
+        <x:v>7610385</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26841,12 +26841,12 @@
         <x:v>205429.02166211</x:v>
       </x:c>
       <x:c>
-        <x:v>328939.77</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>328939.77</x:v>
+        <x:v>329119.77</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>329119.77</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -26877,7 +26877,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>1977619</x:v>
+        <x:v>11017086</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26925,12 +26925,12 @@
         <x:v>137454.57196021</x:v>
       </x:c>
       <x:c>
-        <x:v>196462.56</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>196462.56</x:v>
+        <x:v>197498.43</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>197498.43</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -26961,7 +26961,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>4888744</x:v>
+        <x:v>12551532</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27009,12 +27009,12 @@
         <x:v>228072.49772746</x:v>
       </x:c>
       <x:c>
-        <x:v>308044.18</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>308044.18</x:v>
+        <x:v>308244.77</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>308244.77</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -27045,7 +27045,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>10392445</x:v>
+        <x:v>15375951</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27137,7 +27137,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7853045</x:v>
+        <x:v>302855</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27229,7 +27229,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11858625</x:v>
+        <x:v>13596759</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27285,16 +27285,16 @@
         <x:v>93</x:v>
       </x:c>
       <x:c>
-        <x:v>93359.82</x:v>
-      </x:c>
-      <x:c>
-        <x:v>40.48</x:v>
-      </x:c>
-      <x:c>
-        <x:v>179.91</x:v>
-      </x:c>
-      <x:c>
-        <x:v>93139.43</x:v>
+        <x:v>93391.74</x:v>
+      </x:c>
+      <x:c>
+        <x:v>47.59</x:v>
+      </x:c>
+      <x:c>
+        <x:v>180.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>93163.95</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -27321,7 +27321,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10109593</x:v>
+        <x:v>3261501</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27413,7 +27413,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13781761</x:v>
+        <x:v>10497040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27505,7 +27505,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10154486</x:v>
+        <x:v>16389632</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27597,7 +27597,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8716733</x:v>
+        <x:v>1663849</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27689,7 +27689,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>504583</x:v>
+        <x:v>7112046</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27781,7 +27781,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8587812</x:v>
+        <x:v>1686336</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27873,7 +27873,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1501256</x:v>
+        <x:v>8224659</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27965,7 +27965,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5680232</x:v>
+        <x:v>2441453</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28021,16 +28021,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c>
-        <x:v>55772.76</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1154.55</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>54618.21</x:v>
+        <x:v>55791.45</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1158.29</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>54633.16</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -28057,7 +28057,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4487967</x:v>
+        <x:v>10208742</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28149,7 +28149,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2345886</x:v>
+        <x:v>4232153</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28241,7 +28241,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17451430</x:v>
+        <x:v>10021091</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28333,7 +28333,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7831457</x:v>
+        <x:v>358251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28425,7 +28425,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10111892</x:v>
+        <x:v>15354800</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28517,7 +28517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4756937</x:v>
+        <x:v>2230491</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28609,7 +28609,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4876783</x:v>
+        <x:v>2083263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28701,7 +28701,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8475555</x:v>
+        <x:v>727424</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28793,7 +28793,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3831300</x:v>
+        <x:v>5346763</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28885,7 +28885,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14978628</x:v>
+        <x:v>12551793</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28977,7 +28977,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10661904</x:v>
+        <x:v>16912062</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29069,7 +29069,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11186010</x:v>
+        <x:v>16482411</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29161,7 +29161,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12924841</x:v>
+        <x:v>14687338</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29253,7 +29253,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9541165</x:v>
+        <x:v>14785087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29345,7 +29345,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9125792</x:v>
+        <x:v>15175513</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29437,7 +29437,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7806838</x:v>
+        <x:v>345310</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29505,7 +29505,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>225670</x:v>
+        <x:v>7277072</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29573,7 +29573,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10533440</x:v>
+        <x:v>16778505</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29617,16 +29617,16 @@
         <x:v>375.6534791</x:v>
       </x:c>
       <x:c>
-        <x:v>120158.55</x:v>
-      </x:c>
-      <x:c>
-        <x:v>791.32</x:v>
-      </x:c>
-      <x:c>
-        <x:v>28.1</x:v>
-      </x:c>
-      <x:c>
-        <x:v>119339.13</x:v>
+        <x:v>120226.37</x:v>
+      </x:c>
+      <x:c>
+        <x:v>807.53</x:v>
+      </x:c>
+      <x:c>
+        <x:v>23.9</x:v>
+      </x:c>
+      <x:c>
+        <x:v>119394.94</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -29653,7 +29653,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4451327</x:v>
+        <x:v>6587426</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29733,7 +29733,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15855620</x:v>
+        <x:v>9189251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29813,7 +29813,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1463039</x:v>
+        <x:v>8256927</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29893,7 +29893,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15440129</x:v>
+        <x:v>12831964</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29973,7 +29973,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7893742</x:v>
+        <x:v>954692</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30017,16 +30017,16 @@
         <x:v>1172.9169745</x:v>
       </x:c>
       <x:c>
-        <x:v>52161.63</x:v>
-      </x:c>
-      <x:c>
-        <x:v>360.99</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>51800.64</x:v>
+        <x:v>52189.23</x:v>
+      </x:c>
+      <x:c>
+        <x:v>367.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>51822.03</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -30053,7 +30053,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16491570</x:v>
+        <x:v>9697753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30133,7 +30133,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12426118</x:v>
+        <x:v>14855515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30211,7 +30211,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5670086</x:v>
+        <x:v>3212627</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30289,7 +30289,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9909396</x:v>
+        <x:v>16426955</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30367,7 +30367,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17361931</x:v>
+        <x:v>10952117</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30445,7 +30445,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3455831</x:v>
+        <x:v>5287006</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30523,7 +30523,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9532026</x:v>
+        <x:v>15598800</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30601,7 +30601,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13419384</x:v>
+        <x:v>11601345</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30679,7 +30679,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14648506</x:v>
+        <x:v>12579483</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30757,7 +30757,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13826034</x:v>
+        <x:v>11187158</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30835,7 +30835,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9417497</x:v>
+        <x:v>15735316</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30913,7 +30913,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17240352</x:v>
+        <x:v>11115649</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30983,7 +30983,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7734299</x:v>
+        <x:v>1178823</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31053,7 +31053,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7590711</x:v>
+        <x:v>1305152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31123,7 +31123,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17339882</x:v>
+        <x:v>10947597</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31193,7 +31193,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6560531</x:v>
+        <x:v>4451382</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31263,7 +31263,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3356501</x:v>
+        <x:v>5383487</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31333,7 +31333,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8152424</x:v>
+        <x:v>1887002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31403,7 +31403,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4186489</x:v>
+        <x:v>6759720</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31473,7 +31473,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4599917</x:v>
+        <x:v>6330159</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31541,7 +31541,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2492377</x:v>
+        <x:v>4089546</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31621,7 +31621,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14202980</x:v>
+        <x:v>11185042</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31665,16 +31665,16 @@
         <x:v>16368.71616417</x:v>
       </x:c>
       <x:c>
-        <x:v>19285.47</x:v>
-      </x:c>
-      <x:c>
-        <x:v>125.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>19159.77</x:v>
+        <x:v>19296.08</x:v>
+      </x:c>
+      <x:c>
+        <x:v>128.09</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>19167.99</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -31701,7 +31701,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12222006</x:v>
+        <x:v>13145981</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31769,7 +31769,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25877387</x:v>
+        <x:v>32813999</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31849,7 +31849,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21909812</x:v>
+        <x:v>19769335</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31929,7 +31929,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33225676</x:v>
+        <x:v>27421386</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32009,7 +32009,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24334707</x:v>
+        <x:v>18298342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32077,7 +32077,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23403183</x:v>
+        <x:v>17239933</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32121,16 +32121,16 @@
         <x:v>718.2096246</x:v>
       </x:c>
       <x:c>
-        <x:v>229730.41</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1584.76</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>228145.65</x:v>
+        <x:v>229860.07</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1613.94</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>228246.13</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32157,7 +32157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18087783</x:v>
+        <x:v>24617988</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32201,16 +32201,16 @@
         <x:v>208399.418391</x:v>
       </x:c>
       <x:c>
-        <x:v>304349.55</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2007.93</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>302341.62</x:v>
+        <x:v>304510.67</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2044.18</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>302466.49</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32237,7 +32237,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27519094</x:v>
+        <x:v>33128887</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32281,16 +32281,16 @@
         <x:v>320.0037525</x:v>
       </x:c>
       <x:c>
-        <x:v>457585.56</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2907.71</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>454677.85</x:v>
+        <x:v>457823.19</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2961.17</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>454862.02</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32317,7 +32317,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23100980</x:v>
+        <x:v>20733238</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32361,16 +32361,16 @@
         <x:v>260006.11957</x:v>
       </x:c>
       <x:c>
-        <x:v>344161.96</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2315.63</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>341846.33</x:v>
+        <x:v>344361.47</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2360.52</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>342000.95</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32397,7 +32397,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31866686</x:v>
+        <x:v>25648876</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32477,7 +32477,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30339441</x:v>
+        <x:v>28199140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32521,16 +32521,16 @@
         <x:v>28926.6628967</x:v>
       </x:c>
       <x:c>
-        <x:v>156002.58</x:v>
-      </x:c>
-      <x:c>
-        <x:v>994.49</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>155008.09</x:v>
+        <x:v>156083.93</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1012.79</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>155071.14</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32557,7 +32557,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26658564</x:v>
+        <x:v>32932923</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32637,7 +32637,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31920415</x:v>
+        <x:v>25701794</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32717,7 +32717,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22046943</x:v>
+        <x:v>19712409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32761,16 +32761,16 @@
         <x:v>105585.00641</x:v>
       </x:c>
       <x:c>
-        <x:v>229828.94</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1602.23</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>228226.71</x:v>
+        <x:v>229936.98</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1626.54</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>228310.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32797,7 +32797,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19413630</x:v>
+        <x:v>21248621</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32877,7 +32877,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32550518</x:v>
+        <x:v>26040700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32921,16 +32921,16 @@
         <x:v>3253.3608202</x:v>
       </x:c>
       <x:c>
-        <x:v>456723.48</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2759.41</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>453964.07</x:v>
+        <x:v>456952.84</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2811.01</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>454141.83</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32957,7 +32957,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21331578</x:v>
+        <x:v>19428164</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33001,16 +33001,16 @@
         <x:v>7718.50621968</x:v>
       </x:c>
       <x:c>
-        <x:v>343255.23</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2163.17</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>341092.06</x:v>
+        <x:v>343436.81</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2204.02</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>341232.79</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -33037,7 +33037,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18581404</x:v>
+        <x:v>25124596</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33117,7 +33117,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25720847</x:v>
+        <x:v>31723131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33197,7 +33197,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19793853</x:v>
+        <x:v>21894643</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33289,7 +33289,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29151429</x:v>
+        <x:v>31485597</x:v>
       </x:c>
     </x:row>
     <x:row/>

--- a/posicoes/BTG.xlsx
+++ b/posicoes/BTG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R963670e279ba4f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R720c320c51804257"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -247,7 +247,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32161426</x:v>
+        <x:v>12884654</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -327,7 +327,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21845424</x:v>
+        <x:v>1226250</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -407,7 +407,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24547024</x:v>
+        <x:v>3477508</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -487,7 +487,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32465651</x:v>
+        <x:v>13249119</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -567,7 +567,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17982456</x:v>
+        <x:v>5105038</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -647,7 +647,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18578860</x:v>
+        <x:v>5776450</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -727,7 +727,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24488694</x:v>
+        <x:v>3467277</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -807,7 +807,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23450031</x:v>
+        <x:v>4492616</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -887,7 +887,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28675815</x:v>
+        <x:v>18383946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -943,16 +943,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c>
-        <x:v>187462.92</x:v>
-      </x:c>
-      <x:c>
-        <x:v>7119.43</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>180343.49</x:v>
+        <x:v>187555.7</x:v>
+      </x:c>
+      <x:c>
+        <x:v>7133.35</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>180422.35</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -979,7 +979,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18712018</x:v>
+        <x:v>10361849</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28651286</x:v>
+        <x:v>18349270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1163,7 +1163,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23702163</x:v>
+        <x:v>9440734</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1255,7 +1255,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18717960</x:v>
+        <x:v>3955138</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1347,7 +1347,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17821840</x:v>
+        <x:v>2699238</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1439,7 +1439,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18453593</x:v>
+        <x:v>2019101</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1495,16 +1495,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c>
-        <x:v>89676</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>89676</x:v>
+        <x:v>89715.92</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>89715.92</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -1531,7 +1531,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20661081</x:v>
+        <x:v>3443109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1623,7 +1623,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7367328</x:v>
+        <x:v>18207888</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1715,7 +1715,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19831249</x:v>
+        <x:v>16236021</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1807,7 +1807,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29493376</x:v>
+        <x:v>12086092</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +1899,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27589249</x:v>
+        <x:v>19476428</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1991,7 +1991,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23862665</x:v>
+        <x:v>9369626</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2083,7 +2083,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21215774</x:v>
+        <x:v>19969572</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2175,7 +2175,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20398144</x:v>
+        <x:v>4248518</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2267,7 +2267,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27408060</x:v>
+        <x:v>12781056</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2359,7 +2359,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18158327</x:v>
+        <x:v>19580909</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2451,7 +2451,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22946069</x:v>
+        <x:v>8282603</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2543,7 +2543,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21475304</x:v>
+        <x:v>15090095</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2635,7 +2635,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30528247</x:v>
+        <x:v>17160172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2713,7 +2713,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32249535</x:v>
+        <x:v>12293259</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2757,14 +2757,14 @@
         <x:v>1155</x:v>
       </x:c>
       <x:c>
-        <x:v>112831.95</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>112831.95</x:v>
+        <x:v>112681.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>112681.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2791,7 +2791,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22322632</x:v>
+        <x:v>13097888</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2869,7 +2869,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22123273</x:v>
+        <x:v>1062928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2947,7 +2947,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22712582</x:v>
+        <x:v>1595991</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3017,7 +3017,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24315073</x:v>
+        <x:v>3772044</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3087,7 +3087,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19424924</x:v>
+        <x:v>8980915</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3157,7 +3157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19317006</x:v>
+        <x:v>9400741</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3245,7 +3245,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7401326</x:v>
+        <x:v>6146650</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3313,7 +3313,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21565439</x:v>
+        <x:v>2492067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3393,7 +3393,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22958444</x:v>
+        <x:v>3992921</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3473,7 +3473,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17783862</x:v>
+        <x:v>5448040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3557,7 +3557,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>24970716</x:v>
+        <x:v>16868589</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3641,7 +3641,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>28395649</x:v>
+        <x:v>18604406</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3725,7 +3725,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>17993465</x:v>
+        <x:v>5091258</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3809,7 +3809,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>28489439</x:v>
+        <x:v>18731098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3865,16 +3865,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c>
-        <x:v>25589.03</x:v>
-      </x:c>
-      <x:c>
-        <x:v>978.08</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>24610.95</x:v>
+        <x:v>25604.76</x:v>
+      </x:c>
+      <x:c>
+        <x:v>980.83</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>24623.93</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3901,7 +3901,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7853612</x:v>
+        <x:v>9690550</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3957,16 +3957,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c>
-        <x:v>38561.93</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1498.33</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>37063.6</x:v>
+        <x:v>38584.84</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1502.34</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>37082.5</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3993,7 +3993,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25572949</x:v>
+        <x:v>3446942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4049,16 +4049,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c>
-        <x:v>12759.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>482.89</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>12276.51</x:v>
+        <x:v>12767.12</x:v>
+      </x:c>
+      <x:c>
+        <x:v>484.24</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>12282.88</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -4085,7 +4085,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24645650</x:v>
+        <x:v>15289121</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4177,7 +4177,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27787515</x:v>
+        <x:v>6624024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4269,7 +4269,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25671802</x:v>
+        <x:v>7975365</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4347,7 +4347,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15350645</x:v>
+        <x:v>6636965</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4425,7 +4425,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30866986</x:v>
+        <x:v>10286473</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4503,7 +4503,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20276902</x:v>
+        <x:v>8165085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4581,7 +4581,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18046269</x:v>
+        <x:v>5163880</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4659,7 +4659,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25147983</x:v>
+        <x:v>16362384</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4737,7 +4737,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25510780</x:v>
+        <x:v>17600003</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4815,7 +4815,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17320327</x:v>
+        <x:v>5264225</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4893,7 +4893,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27369703</x:v>
+        <x:v>19826331</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4971,7 +4971,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23994206</x:v>
+        <x:v>2978408</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5049,7 +5049,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17027315</x:v>
+        <x:v>6755578</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5127,7 +5127,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15008594</x:v>
+        <x:v>7044471</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5205,7 +5205,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27670430</x:v>
+        <x:v>19544025</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5283,7 +5283,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30475986</x:v>
+        <x:v>10426013</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5361,7 +5361,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27143372</x:v>
+        <x:v>18890571</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5439,7 +5439,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22413574</x:v>
+        <x:v>1735095</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5517,7 +5517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23756579</x:v>
+        <x:v>3217234</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5595,7 +5595,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32388234</x:v>
+        <x:v>12455501</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5673,7 +5673,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27009852</x:v>
+        <x:v>19370228</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5743,7 +5743,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17580015</x:v>
+        <x:v>5380598</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5813,7 +5813,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28417513</x:v>
+        <x:v>18650145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5883,7 +5883,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27566228</x:v>
+        <x:v>20104928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5953,7 +5953,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30105609</x:v>
+        <x:v>10015144</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6023,7 +6023,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19383600</x:v>
+        <x:v>9464461</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6093,7 +6093,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18903415</x:v>
+        <x:v>8395002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6163,7 +6163,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28572383</x:v>
+        <x:v>18295163</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6233,7 +6233,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29183462</x:v>
+        <x:v>10670939</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6303,7 +6303,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31456045</x:v>
+        <x:v>14461227</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6373,7 +6373,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21550461</x:v>
+        <x:v>2442256</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6443,7 +6443,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22655051</x:v>
+        <x:v>1527365</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6513,7 +6513,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20660890</x:v>
+        <x:v>7885036</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6581,7 +6581,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29706245</x:v>
+        <x:v>12221949</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6661,7 +6661,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21533495</x:v>
+        <x:v>3090568</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6741,7 +6741,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21743953</x:v>
+        <x:v>3266875</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6821,7 +6821,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19333127</x:v>
+        <x:v>10319789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6901,7 +6901,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22245476</x:v>
+        <x:v>1605558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6981,7 +6981,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25479630</x:v>
+        <x:v>17477462</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7061,7 +7061,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26153479</x:v>
+        <x:v>16265861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7141,7 +7141,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33071922</x:v>
+        <x:v>13855612</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7221,7 +7221,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23202089</x:v>
+        <x:v>5176486</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7301,7 +7301,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21074252</x:v>
+        <x:v>2526661</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7381,7 +7381,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27066839</x:v>
+        <x:v>20248771</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7461,7 +7461,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30793559</x:v>
+        <x:v>11790725</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7545,7 +7545,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>21995961</x:v>
+        <x:v>1862826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7629,7 +7629,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>22743235</x:v>
+        <x:v>2008522</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7685,16 +7685,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c>
-        <x:v>9543.92</x:v>
-      </x:c>
-      <x:c>
-        <x:v>122.38</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>9421.54</x:v>
+        <x:v>9548.96</x:v>
+      </x:c>
+      <x:c>
+        <x:v>123.51</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>9425.45</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7721,7 +7721,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29605480</x:v>
+        <x:v>8943150</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7777,16 +7777,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c>
-        <x:v>54734.52</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1528.54</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>53205.98</x:v>
+        <x:v>54765.23</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1533.91</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>53231.32</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7813,7 +7813,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26470355</x:v>
+        <x:v>16443251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7869,16 +7869,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c>
-        <x:v>51463.57</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>51463.57</x:v>
+        <x:v>51487.81</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>51487.81</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7905,7 +7905,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19181867</x:v>
+        <x:v>9483525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7961,16 +7961,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c>
-        <x:v>9227.01</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>9227.01</x:v>
+        <x:v>9231.42</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>9231.42</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -7997,7 +7997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26624982</x:v>
+        <x:v>16947008</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8089,7 +8089,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22241615</x:v>
+        <x:v>17858589</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8181,7 +8181,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30719542</x:v>
+        <x:v>17840800</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8225,14 +8225,14 @@
         <x:v>116</x:v>
       </x:c>
       <x:c>
-        <x:v>6149.16</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6149.16</x:v>
+        <x:v>6153.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6153.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8259,7 +8259,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18105511</x:v>
+        <x:v>12565349</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8337,7 +8337,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27203466</x:v>
+        <x:v>20377214</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8381,14 +8381,14 @@
         <x:v>132</x:v>
       </x:c>
       <x:c>
-        <x:v>5921.52</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>5921.52</x:v>
+        <x:v>5913.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>5913.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8415,7 +8415,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27920812</x:v>
+        <x:v>4496973</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8493,7 +8493,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18383060</x:v>
+        <x:v>6747262</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8537,14 +8537,14 @@
         <x:v>135</x:v>
       </x:c>
       <x:c>
-        <x:v>5042.25</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>5042.25</x:v>
+        <x:v>5032.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>5032.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8571,7 +8571,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30292115</x:v>
+        <x:v>2829793</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8649,7 +8649,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10534822</x:v>
+        <x:v>7834971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8693,14 +8693,14 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c>
-        <x:v>15573.16</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>15573.16</x:v>
+        <x:v>15561.38</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>15561.38</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8727,7 +8727,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26965663</x:v>
+        <x:v>4285440</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8771,14 +8771,14 @@
         <x:v>337</x:v>
       </x:c>
       <x:c>
-        <x:v>14743.75</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>14743.75</x:v>
+        <x:v>14710.05</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>14710.05</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8805,7 +8805,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20903749</x:v>
+        <x:v>14130423</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8849,14 +8849,14 @@
         <x:v>122</x:v>
       </x:c>
       <x:c>
-        <x:v>54135.06</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>54135.06</x:v>
+        <x:v>54210.7</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>54210.7</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -8883,7 +8883,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30296667</x:v>
+        <x:v>10673024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8961,7 +8961,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24158516</x:v>
+        <x:v>4030360</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9039,7 +9039,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25234479</x:v>
+        <x:v>17776078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9083,14 +9083,14 @@
         <x:v>2754</x:v>
       </x:c>
       <x:c>
-        <x:v>58054.32</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>58054.32</x:v>
+        <x:v>57834</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>57834</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9117,7 +9117,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28559910</x:v>
+        <x:v>5204339</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9161,14 +9161,14 @@
         <x:v>4582</x:v>
       </x:c>
       <x:c>
-        <x:v>34410.82</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>34410.82</x:v>
+        <x:v>34044.26</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>34044.26</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9195,7 +9195,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28140097</x:v>
+        <x:v>12051874</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9239,14 +9239,14 @@
         <x:v>230</x:v>
       </x:c>
       <x:c>
-        <x:v>6187</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6187</x:v>
+        <x:v>6184.7</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6184.7</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9273,7 +9273,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32289974</x:v>
+        <x:v>3801528</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9351,7 +9351,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30893597</x:v>
+        <x:v>11886067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9395,14 +9395,14 @@
         <x:v>550</x:v>
       </x:c>
       <x:c>
-        <x:v>38984</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>38984</x:v>
+        <x:v>38978.5</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>38978.5</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9429,7 +9429,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27549192</x:v>
+        <x:v>20030371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9473,14 +9473,14 @@
         <x:v>420</x:v>
       </x:c>
       <x:c>
-        <x:v>41029.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>41029.8</x:v>
+        <x:v>40975.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>40975.2</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9507,7 +9507,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26074752</x:v>
+        <x:v>8362994</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9551,14 +9551,14 @@
         <x:v>81</x:v>
       </x:c>
       <x:c>
-        <x:v>6876.9</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6876.9</x:v>
+        <x:v>6847.74</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6847.74</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9585,7 +9585,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26952100</x:v>
+        <x:v>19907001</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9663,7 +9663,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28349358</x:v>
+        <x:v>18881707</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9741,7 +9741,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28574013</x:v>
+        <x:v>18588594</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9819,7 +9819,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29112646</x:v>
+        <x:v>19372966</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9897,7 +9897,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32090847</x:v>
+        <x:v>15062094</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9975,7 +9975,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32735922</x:v>
+        <x:v>13284178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10019,14 +10019,14 @@
         <x:v>306</x:v>
       </x:c>
       <x:c>
-        <x:v>35496</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>35496</x:v>
+        <x:v>35587.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>35587.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10053,7 +10053,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29534963</x:v>
+        <x:v>13556855</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10131,7 +10131,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28419077</x:v>
+        <x:v>19046433</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10209,7 +10209,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24465910</x:v>
+        <x:v>3839087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10253,14 +10253,14 @@
         <x:v>857</x:v>
       </x:c>
       <x:c>
-        <x:v>7721.57</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7721.57</x:v>
+        <x:v>7713</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7713</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10287,7 +10287,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25340533</x:v>
+        <x:v>10513211</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10365,7 +10365,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32337754</x:v>
+        <x:v>13439398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10443,7 +10443,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20212902</x:v>
+        <x:v>8403414</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10513,7 +10513,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29326870</x:v>
+        <x:v>12342249</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10583,7 +10583,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23576989</x:v>
+        <x:v>5597900</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10653,7 +10653,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19131491</x:v>
+        <x:v>9476026</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10723,7 +10723,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25123327</x:v>
+        <x:v>17648488</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10793,7 +10793,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17186555</x:v>
+        <x:v>7712586</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10863,7 +10863,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22754217</x:v>
+        <x:v>2066984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10933,7 +10933,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27461395</x:v>
+        <x:v>20037564</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11003,7 +11003,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33121169</x:v>
+        <x:v>13955669</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11073,7 +11073,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27498555</x:v>
+        <x:v>20108269</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11143,7 +11143,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29759654</x:v>
+        <x:v>12907767</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11213,7 +11213,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20639591</x:v>
+        <x:v>8912475</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11283,7 +11283,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21254560</x:v>
+        <x:v>2785998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11353,7 +11353,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23644119</x:v>
+        <x:v>5655411</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11423,7 +11423,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30154143</x:v>
+        <x:v>12741888</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11493,7 +11493,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17769638</x:v>
+        <x:v>6192202</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11563,7 +11563,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29035872</x:v>
+        <x:v>19201445</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11633,7 +11633,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27811099</x:v>
+        <x:v>20808146</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11703,7 +11703,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27938836</x:v>
+        <x:v>20483208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11771,7 +11771,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2774354</x:v>
+        <x:v>23914553</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11851,7 +11851,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11764072</x:v>
+        <x:v>32213971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11931,7 +11931,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13786656</x:v>
+        <x:v>26059942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12011,7 +12011,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15546353</x:v>
+        <x:v>27597224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12067,16 +12067,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c>
-        <x:v>107280.41</x:v>
-      </x:c>
-      <x:c>
-        <x:v>4092.06</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>103188.35</x:v>
+        <x:v>107333.96</x:v>
+      </x:c>
+      <x:c>
+        <x:v>4100.09</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>103233.87</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12103,7 +12103,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>206906</x:v>
+        <x:v>25705644</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12195,7 +12195,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15797763</x:v>
+        <x:v>8127015</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12287,7 +12287,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8161041</x:v>
+        <x:v>30399173</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12365,7 +12365,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3473079</x:v>
+        <x:v>22537256</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12443,7 +12443,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14035631</x:v>
+        <x:v>24723681</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12521,7 +12521,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7612886</x:v>
+        <x:v>11609745</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12599,7 +12599,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9566671</x:v>
+        <x:v>30214269</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12677,7 +12677,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10571547</x:v>
+        <x:v>29055690</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12755,7 +12755,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13834766</x:v>
+        <x:v>26077777</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12833,7 +12833,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3173048</x:v>
+        <x:v>22770014</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12911,7 +12911,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11503412</x:v>
+        <x:v>32454012</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12989,7 +12989,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>560053</x:v>
+        <x:v>21874237</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13067,7 +13067,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5848613</x:v>
+        <x:v>702864</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13145,7 +13145,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15386217</x:v>
+        <x:v>27940440</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13223,7 +13223,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16216610</x:v>
+        <x:v>28215726</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13301,7 +13301,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13345339</x:v>
+        <x:v>25586145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13379,7 +13379,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11260221</x:v>
+        <x:v>31757600</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13457,7 +13457,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12127625</x:v>
+        <x:v>30552043</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13535,7 +13535,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4554910</x:v>
+        <x:v>971340</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13613,7 +13613,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12363969</x:v>
+        <x:v>30778457</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13691,7 +13691,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3229635</x:v>
+        <x:v>22840954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13761,7 +13761,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17464282</x:v>
+        <x:v>27169336</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13831,7 +13831,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5576839</x:v>
+        <x:v>111853</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13901,7 +13901,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4219195</x:v>
+        <x:v>1543777</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13971,7 +13971,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3674877</x:v>
+        <x:v>23298234</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14041,7 +14041,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13062296</x:v>
+        <x:v>25854236</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14111,7 +14111,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15204189</x:v>
+        <x:v>27799218</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14181,7 +14181,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8039725</x:v>
+        <x:v>14069338</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14251,7 +14251,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>54762</x:v>
+        <x:v>21728236</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14321,7 +14321,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2816063</x:v>
+        <x:v>23939565</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14391,7 +14391,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9139173</x:v>
+        <x:v>30306889</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14461,7 +14461,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6183062</x:v>
+        <x:v>480318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14529,7 +14529,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24696350</x:v>
+        <x:v>3658404</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14609,7 +14609,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30471942</x:v>
+        <x:v>10431300</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14677,7 +14677,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30125921</x:v>
+        <x:v>9509855</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14757,7 +14757,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19626377</x:v>
+        <x:v>9230334</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14837,7 +14837,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30223391</x:v>
+        <x:v>9602010</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14917,7 +14917,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23910869</x:v>
+        <x:v>3381839</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14997,7 +14997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31135287</x:v>
+        <x:v>14002036</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15077,7 +15077,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30278558</x:v>
+        <x:v>9682108</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15157,7 +15157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31841798</x:v>
+        <x:v>14350251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15237,7 +15237,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27414473</x:v>
+        <x:v>19849833</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15317,7 +15317,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30422111</x:v>
+        <x:v>10341938</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15401,7 +15401,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>18138567</x:v>
+        <x:v>5849118</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15485,7 +15485,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>24612614</x:v>
+        <x:v>3539319</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15541,16 +15541,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c>
-        <x:v>199229.52</x:v>
-      </x:c>
-      <x:c>
-        <x:v>8884.42</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>190345.1</x:v>
+        <x:v>199353.54</x:v>
+      </x:c>
+      <x:c>
+        <x:v>8903.03</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>190450.51</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15577,7 +15577,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24973837</x:v>
+        <x:v>6167515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15633,16 +15633,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c>
-        <x:v>94318.77</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>94318.77</x:v>
+        <x:v>94367.01</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>94367.01</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -15669,7 +15669,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21705305</x:v>
+        <x:v>5135679</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15761,7 +15761,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20296988</x:v>
+        <x:v>4325914</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15853,7 +15853,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19875603</x:v>
+        <x:v>4781872</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15945,7 +15945,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18755123</x:v>
+        <x:v>3797891</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16037,7 +16037,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25878297</x:v>
+        <x:v>12070714</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16129,7 +16129,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21101743</x:v>
+        <x:v>5638995</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16221,7 +16221,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29560135</x:v>
+        <x:v>15102514</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16313,7 +16313,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7334171</x:v>
+        <x:v>1011810</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16405,7 +16405,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20144396</x:v>
+        <x:v>14203110</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16497,7 +16497,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10468508</x:v>
+        <x:v>6836530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16589,7 +16589,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24539499</x:v>
+        <x:v>12090264</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16681,7 +16681,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23601943</x:v>
+        <x:v>17632923</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16773,7 +16773,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25688465</x:v>
+        <x:v>1020465</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16865,7 +16865,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24885321</x:v>
+        <x:v>7101299</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16957,7 +16957,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25830899</x:v>
+        <x:v>15081990</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17049,7 +17049,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24079001</x:v>
+        <x:v>15755785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17141,7 +17141,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22180025</x:v>
+        <x:v>13779988</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17233,7 +17233,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28789739</x:v>
+        <x:v>6908135</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17325,7 +17325,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18345269</x:v>
+        <x:v>17144725</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17417,7 +17417,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20150829</x:v>
+        <x:v>19352546</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17509,7 +17509,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18394958</x:v>
+        <x:v>17427240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17601,7 +17601,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30515416</x:v>
+        <x:v>1044363</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17693,7 +17693,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22238336</x:v>
+        <x:v>3057219</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17785,7 +17785,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18668906</x:v>
+        <x:v>13330716</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17829,14 +17829,14 @@
         <x:v>600</x:v>
       </x:c>
       <x:c>
-        <x:v>10848</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>10848</x:v>
+        <x:v>10842</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>10842</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17863,7 +17863,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31387910</x:v>
+        <x:v>19560247</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17907,14 +17907,14 @@
         <x:v>140</x:v>
       </x:c>
       <x:c>
-        <x:v>7421.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7421.4</x:v>
+        <x:v>7427</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7427</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17941,7 +17941,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18510310</x:v>
+        <x:v>12170259</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18019,7 +18019,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23298626</x:v>
+        <x:v>4893693</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18063,14 +18063,14 @@
         <x:v>385</x:v>
       </x:c>
       <x:c>
-        <x:v>37737.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>37737.7</x:v>
+        <x:v>37895.55</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>37895.55</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -18097,7 +18097,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23977935</x:v>
+        <x:v>16341460</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18141,14 +18141,14 @@
         <x:v>161</x:v>
       </x:c>
       <x:c>
-        <x:v>2398.9</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>2398.9</x:v>
+        <x:v>2406.95</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>2406.95</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -18175,7 +18175,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23312366</x:v>
+        <x:v>7751929</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18219,14 +18219,14 @@
         <x:v>200</x:v>
       </x:c>
       <x:c>
-        <x:v>4010</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>4010</x:v>
+        <x:v>4012</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>4012</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -18253,7 +18253,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29192372</x:v>
+        <x:v>14446132</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18331,7 +18331,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29745244</x:v>
+        <x:v>11505132</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18375,14 +18375,14 @@
         <x:v>56</x:v>
       </x:c>
       <x:c>
-        <x:v>3015.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>3015.6</x:v>
+        <x:v>3018.96</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>3018.96</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -18409,7 +18409,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27206967</x:v>
+        <x:v>2231951</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18453,14 +18453,14 @@
         <x:v>1560</x:v>
       </x:c>
       <x:c>
-        <x:v>17050.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>17050.8</x:v>
+        <x:v>17035.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>17035.2</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -18487,7 +18487,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24142724</x:v>
+        <x:v>18902418</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18531,14 +18531,14 @@
         <x:v>501</x:v>
       </x:c>
       <x:c>
-        <x:v>22474.86</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>22474.86</x:v>
+        <x:v>22444.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>22444.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -18565,7 +18565,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6870952</x:v>
+        <x:v>9919471</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18609,14 +18609,14 @@
         <x:v>1300</x:v>
       </x:c>
       <x:c>
-        <x:v>19188</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>19188</x:v>
+        <x:v>19071</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>19071</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -18643,7 +18643,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21175096</x:v>
+        <x:v>7197790</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18721,7 +18721,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28989369</x:v>
+        <x:v>11181128</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18765,14 +18765,14 @@
         <x:v>231</x:v>
       </x:c>
       <x:c>
-        <x:v>8627.85</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8627.85</x:v>
+        <x:v>8611.68</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8611.68</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -18799,7 +18799,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31458824</x:v>
+        <x:v>3784586</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18843,14 +18843,14 @@
         <x:v>1320</x:v>
       </x:c>
       <x:c>
-        <x:v>32920.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>32920.8</x:v>
+        <x:v>33066</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>33066</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -18877,7 +18877,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29107880</x:v>
+        <x:v>19465539</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18955,7 +18955,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26336829</x:v>
+        <x:v>15742827</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18999,14 +18999,14 @@
         <x:v>1252</x:v>
       </x:c>
       <x:c>
-        <x:v>16551.44</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>16551.44</x:v>
+        <x:v>16538.92</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>16538.92</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19033,7 +19033,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29867224</x:v>
+        <x:v>7421196</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19077,14 +19077,14 @@
         <x:v>262</x:v>
       </x:c>
       <x:c>
-        <x:v>11462.5</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>11462.5</x:v>
+        <x:v>11436.3</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>11436.3</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19111,7 +19111,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21051449</x:v>
+        <x:v>13119015</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19155,14 +19155,14 @@
         <x:v>217</x:v>
       </x:c>
       <x:c>
-        <x:v>96289.41</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>96289.41</x:v>
+        <x:v>96423.95</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>96423.95</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19189,7 +19189,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32420879</x:v>
+        <x:v>12729216</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19267,7 +19267,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27802547</x:v>
+        <x:v>18003318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19345,7 +19345,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19780164</x:v>
+        <x:v>7461519</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19389,14 +19389,14 @@
         <x:v>3696</x:v>
       </x:c>
       <x:c>
-        <x:v>77911.68</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>77911.68</x:v>
+        <x:v>77616</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>77616</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19423,7 +19423,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9896580</x:v>
+        <x:v>10131699</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19467,14 +19467,14 @@
         <x:v>45</x:v>
       </x:c>
       <x:c>
-        <x:v>2272.5</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>2272.5</x:v>
+        <x:v>2268.9</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>2268.9</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19501,7 +19501,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28976066</x:v>
+        <x:v>2985805</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19545,14 +19545,14 @@
         <x:v>965</x:v>
       </x:c>
       <x:c>
-        <x:v>7247.15</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7247.15</x:v>
+        <x:v>7169.95</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7169.95</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19579,7 +19579,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28439728</x:v>
+        <x:v>9891323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19623,14 +19623,14 @@
         <x:v>786</x:v>
       </x:c>
       <x:c>
-        <x:v>21143.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>21143.4</x:v>
+        <x:v>21135.54</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>21135.54</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19657,7 +19657,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23033809</x:v>
+        <x:v>13070625</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19701,14 +19701,14 @@
         <x:v>600</x:v>
       </x:c>
       <x:c>
-        <x:v>23694</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>23694</x:v>
+        <x:v>23550</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>23550</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19735,7 +19735,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27823688</x:v>
+        <x:v>17401638</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19779,14 +19779,14 @@
         <x:v>440</x:v>
       </x:c>
       <x:c>
-        <x:v>26488</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>26488</x:v>
+        <x:v>26461.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>26461.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -19813,7 +19813,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25288406</x:v>
+        <x:v>5538776</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19891,7 +19891,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21486106</x:v>
+        <x:v>2881337</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19969,7 +19969,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27600876</x:v>
+        <x:v>19445440</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20013,14 +20013,14 @@
         <x:v>348</x:v>
       </x:c>
       <x:c>
-        <x:v>24666.24</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>24666.24</x:v>
+        <x:v>24662.76</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>24662.76</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20047,7 +20047,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30581510</x:v>
+        <x:v>10459200</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20091,14 +20091,14 @@
         <x:v>612</x:v>
       </x:c>
       <x:c>
-        <x:v>59786.28</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>59786.28</x:v>
+        <x:v>59706.72</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>59706.72</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20125,7 +20125,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32276326</x:v>
+        <x:v>1324792</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20169,14 +20169,14 @@
         <x:v>93</x:v>
       </x:c>
       <x:c>
-        <x:v>7895.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7895.7</x:v>
+        <x:v>7862.22</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7862.22</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20203,7 +20203,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30106019</x:v>
+        <x:v>14454099</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20281,7 +20281,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27275713</x:v>
+        <x:v>19016862</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20359,7 +20359,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22707506</x:v>
+        <x:v>1602117</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20437,7 +20437,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30133820</x:v>
+        <x:v>9502788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20515,7 +20515,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19256934</x:v>
+        <x:v>9332538</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20593,7 +20593,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17068294</x:v>
+        <x:v>6775339</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20671,7 +20671,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29054527</x:v>
+        <x:v>11277660</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20715,14 +20715,14 @@
         <x:v>229</x:v>
       </x:c>
       <x:c>
-        <x:v>26564</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>26564</x:v>
+        <x:v>26632.7</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>26632.7</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20749,7 +20749,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26407137</x:v>
+        <x:v>19541455</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20827,7 +20827,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22806258</x:v>
+        <x:v>4298990</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20905,7 +20905,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31945863</x:v>
+        <x:v>12666631</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20949,14 +20949,14 @@
         <x:v>991</x:v>
       </x:c>
       <x:c>
-        <x:v>8928.91</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8928.91</x:v>
+        <x:v>8919</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8919</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20983,7 +20983,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31589003</x:v>
+        <x:v>18712588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21061,7 +21061,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20227957</x:v>
+        <x:v>8029693</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21139,7 +21139,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23067493</x:v>
+        <x:v>4059781</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21209,7 +21209,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20345201</x:v>
+        <x:v>8251748</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21279,7 +21279,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25414984</x:v>
+        <x:v>17490366</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21349,7 +21349,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18743310</x:v>
+        <x:v>8820083</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21419,7 +21419,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17052097</x:v>
+        <x:v>6726864</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21489,7 +21489,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32823314</x:v>
+        <x:v>13092485</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21559,7 +21559,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26769544</x:v>
+        <x:v>15638551</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21629,7 +21629,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19303904</x:v>
+        <x:v>9415841</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21699,7 +21699,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29624929</x:v>
+        <x:v>11295050</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21769,7 +21769,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18843799</x:v>
+        <x:v>8911036</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21839,7 +21839,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18792816</x:v>
+        <x:v>8836485</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21909,7 +21909,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29234978</x:v>
+        <x:v>10744868</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21979,7 +21979,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22582223</x:v>
+        <x:v>1426728</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22049,7 +22049,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26053153</x:v>
+        <x:v>15362546</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22119,7 +22119,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28484868</x:v>
+        <x:v>18735908</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22189,7 +22189,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31626620</x:v>
+        <x:v>14794966</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22259,7 +22259,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17851798</x:v>
+        <x:v>5508954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22329,7 +22329,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22065638</x:v>
+        <x:v>1025395</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22399,7 +22399,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22200067</x:v>
+        <x:v>1096287</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22469,7 +22469,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17836153</x:v>
+        <x:v>5456613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22539,7 +22539,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30001211</x:v>
+        <x:v>9936422</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22609,7 +22609,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30071460</x:v>
+        <x:v>9987592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22679,7 +22679,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25459643</x:v>
+        <x:v>17519223</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22749,7 +22749,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31195667</x:v>
+        <x:v>13486003</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22819,7 +22819,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17769246</x:v>
+        <x:v>5398969</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22889,7 +22889,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23418811</x:v>
+        <x:v>4973219</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22959,7 +22959,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21127041</x:v>
+        <x:v>2067093</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23029,7 +23029,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31041717</x:v>
+        <x:v>13966228</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23099,7 +23099,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18256716</x:v>
+        <x:v>5912534</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23169,7 +23169,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25873273</x:v>
+        <x:v>15160303</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23239,7 +23239,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25172708</x:v>
+        <x:v>16424335</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23309,7 +23309,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24812240</x:v>
+        <x:v>16599306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23377,7 +23377,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10111400</x:v>
+        <x:v>29933900</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23457,7 +23457,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16196159</x:v>
+        <x:v>29375289</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23513,16 +23513,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c>
-        <x:v>16125.21</x:v>
-      </x:c>
-      <x:c>
-        <x:v>546.91</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>15578.3</x:v>
+        <x:v>16134.62</x:v>
+      </x:c>
+      <x:c>
+        <x:v>548.55</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>15586.07</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23549,7 +23549,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13316703</x:v>
+        <x:v>32743161</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23641,7 +23641,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10636981</x:v>
+        <x:v>26415148</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23697,16 +23697,16 @@
         <x:v>170</x:v>
       </x:c>
       <x:c>
-        <x:v>214338.83</x:v>
-      </x:c>
-      <x:c>
-        <x:v>7759.29</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>206579.54</x:v>
+        <x:v>214442.13</x:v>
+      </x:c>
+      <x:c>
+        <x:v>7777.37</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>206664.76</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23733,7 +23733,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12221125</x:v>
+        <x:v>21617077</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23825,7 +23825,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2075023</x:v>
+        <x:v>32724039</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23881,16 +23881,16 @@
         <x:v>206</x:v>
       </x:c>
       <x:c>
-        <x:v>257056.49</x:v>
-      </x:c>
-      <x:c>
-        <x:v>8934.88</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>248121.61</x:v>
+        <x:v>257174.85</x:v>
+      </x:c>
+      <x:c>
+        <x:v>8955.59</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>248219.26</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23917,7 +23917,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12625293</x:v>
+        <x:v>14525315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24009,7 +24009,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9518273</x:v>
+        <x:v>24477814</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24065,16 +24065,16 @@
         <x:v>195</x:v>
       </x:c>
       <x:c>
-        <x:v>244779.76</x:v>
-      </x:c>
-      <x:c>
-        <x:v>8711.45</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>236068.31</x:v>
+        <x:v>244895.49</x:v>
+      </x:c>
+      <x:c>
+        <x:v>8731.71</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>236163.78</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24101,7 +24101,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10641598</x:v>
+        <x:v>25622085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24157,16 +24157,16 @@
         <x:v>170</x:v>
       </x:c>
       <x:c>
-        <x:v>215245.58</x:v>
-      </x:c>
-      <x:c>
-        <x:v>7917.97</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>207327.61</x:v>
+        <x:v>215351.21</x:v>
+      </x:c>
+      <x:c>
+        <x:v>7936.46</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>207414.75</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24193,7 +24193,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16615907</x:v>
+        <x:v>32375938</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24249,16 +24249,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c>
-        <x:v>122042.83</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>122042.83</x:v>
+        <x:v>122102.73</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>122102.73</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24285,7 +24285,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9118536</x:v>
+        <x:v>29577960</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24341,16 +24341,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c>
-        <x:v>72950.48</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>72950.48</x:v>
+        <x:v>72986.47</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>72986.47</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24377,7 +24377,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2222403</x:v>
+        <x:v>27911789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24433,16 +24433,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c>
-        <x:v>28142.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>28142.4</x:v>
+        <x:v>28156.28</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>28156.28</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24469,7 +24469,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2698132</x:v>
+        <x:v>29765900</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24525,16 +24525,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c>
-        <x:v>69703.66</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>69703.66</x:v>
+        <x:v>69737.24</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>69737.24</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24561,7 +24561,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>252230</x:v>
+        <x:v>32626082</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24617,16 +24617,16 @@
         <x:v>150000</x:v>
       </x:c>
       <x:c>
-        <x:v>184815.79</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>184815.79</x:v>
+        <x:v>184907.45</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>184907.45</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -24653,7 +24653,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14517127</x:v>
+        <x:v>29797612</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24731,7 +24731,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5572981</x:v>
+        <x:v>11651722</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24799,7 +24799,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29692414</x:v>
+        <x:v>11479063</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24883,7 +24883,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>23614486</x:v>
+        <x:v>4661408</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24951,7 +24951,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27348790</x:v>
+        <x:v>19788165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25035,7 +25035,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>23785440</x:v>
+        <x:v>3251617</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25103,7 +25103,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25142118</x:v>
+        <x:v>16369679</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25183,7 +25183,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30381437</x:v>
+        <x:v>10324639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25263,7 +25263,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25687578</x:v>
+        <x:v>17084035</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25343,7 +25343,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26190681</x:v>
+        <x:v>14961742</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25423,7 +25423,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31898802</x:v>
+        <x:v>14416161</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25503,7 +25503,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26313145</x:v>
+        <x:v>15031526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25571,7 +25571,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28307157</x:v>
+        <x:v>18561706</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25651,7 +25651,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30738415</x:v>
+        <x:v>10149193</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25731,7 +25731,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22265261</x:v>
+        <x:v>1140313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25809,7 +25809,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18729355</x:v>
+        <x:v>8759686</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25879,7 +25879,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28908483</x:v>
+        <x:v>10975975</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25947,7 +25947,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4040522</x:v>
+        <x:v>23140886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26027,7 +26027,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12677069</x:v>
+        <x:v>31041098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26119,7 +26119,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16747935</x:v>
+        <x:v>596881</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26175,16 +26175,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c>
-        <x:v>2372.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>65.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2307.4</x:v>
+        <x:v>2373.91</x:v>
+      </x:c>
+      <x:c>
+        <x:v>65.43</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2308.48</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -26211,7 +26211,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11346044</x:v>
+        <x:v>24011299</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26279,7 +26279,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27450433</x:v>
+        <x:v>19939414</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26347,7 +26347,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31617773</x:v>
+        <x:v>14490896</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26415,7 +26415,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16073654</x:v>
+        <x:v>28095496</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26499,7 +26499,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>7601725</x:v>
+        <x:v>11505877</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26583,7 +26583,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>9890519</x:v>
+        <x:v>28509039</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26667,7 +26667,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>13336741</x:v>
+        <x:v>25595484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26751,7 +26751,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>5688623</x:v>
+        <x:v>539178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26835,7 +26835,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>5392470</x:v>
+        <x:v>10416</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26927,7 +26927,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8633609</x:v>
+        <x:v>29845248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27019,7 +27019,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8624886</x:v>
+        <x:v>29854200</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27111,7 +27111,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15838827</x:v>
+        <x:v>9910734</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27203,7 +27203,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6250273</x:v>
+        <x:v>28873213</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27259,16 +27259,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c>
-        <x:v>39157.01</x:v>
-      </x:c>
-      <x:c>
-        <x:v>831.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>38325.61</x:v>
+        <x:v>39177.65</x:v>
+      </x:c>
+      <x:c>
+        <x:v>835.53</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>38342.12</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -27295,7 +27295,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7045252</x:v>
+        <x:v>30143679</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27351,16 +27351,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c>
-        <x:v>39518.45</x:v>
-      </x:c>
-      <x:c>
-        <x:v>903.69</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>38614.76</x:v>
+        <x:v>39539.89</x:v>
+      </x:c>
+      <x:c>
+        <x:v>907.97</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>38631.92</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -27387,7 +27387,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6875511</x:v>
+        <x:v>25922696</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27479,7 +27479,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1421408</x:v>
+        <x:v>20199097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27571,7 +27571,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2757766</x:v>
+        <x:v>24094453</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27627,16 +27627,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c>
-        <x:v>56404.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1280.94</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>55123.76</x:v>
+        <x:v>56435.08</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1287.01</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>55148.07</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -27663,7 +27663,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13713316</x:v>
+        <x:v>24285180</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27719,16 +27719,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c>
-        <x:v>55698.37</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1139.67</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>54558.7</x:v>
+        <x:v>55726.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1145.32</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>54581.28</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -27755,7 +27755,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12496933</x:v>
+        <x:v>27968520</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27847,7 +27847,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5278278</x:v>
+        <x:v>31992071</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27939,7 +27939,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6832937</x:v>
+        <x:v>29591785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28031,7 +28031,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8708676</x:v>
+        <x:v>27704291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28123,7 +28123,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15740660</x:v>
+        <x:v>31006669</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28215,7 +28215,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13247118</x:v>
+        <x:v>21061462</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28307,7 +28307,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31139</x:v>
+        <x:v>730998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28399,7 +28399,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1145382</x:v>
+        <x:v>31615523</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28491,7 +28491,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9993750</x:v>
+        <x:v>26145921</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28583,7 +28583,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10259326</x:v>
+        <x:v>25824007</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28675,7 +28675,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11319602</x:v>
+        <x:v>21034492</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28767,7 +28767,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5195997</x:v>
+        <x:v>22242590</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28859,7 +28859,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7968358</x:v>
+        <x:v>23968573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28951,7 +28951,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10142711</x:v>
+        <x:v>29333234</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29043,7 +29043,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4079423</x:v>
+        <x:v>21348055</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29135,7 +29135,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4735749</x:v>
+        <x:v>31778421</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29227,7 +29227,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2108182</x:v>
+        <x:v>23857266</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29295,7 +29295,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9012707</x:v>
+        <x:v>30961875</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29363,7 +29363,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3308733</x:v>
+        <x:v>24807086</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29443,7 +29443,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4326901</x:v>
+        <x:v>23735700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29523,7 +29523,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13210649</x:v>
+        <x:v>32315875</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29603,7 +29603,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14869031</x:v>
+        <x:v>25528812</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29683,7 +29683,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14155286</x:v>
+        <x:v>26913114</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29763,7 +29763,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6727498</x:v>
+        <x:v>19301086</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29843,7 +29843,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9202801</x:v>
+        <x:v>31104371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29923,7 +29923,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16319095</x:v>
+        <x:v>29452744</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30001,7 +30001,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>351065</x:v>
+        <x:v>22522886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30079,7 +30079,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7126515</x:v>
+        <x:v>17976853</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30157,7 +30157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5711329</x:v>
+        <x:v>627638</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30235,7 +30235,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12481523</x:v>
+        <x:v>32154486</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30313,7 +30313,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3813128</x:v>
+        <x:v>23261286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30391,7 +30391,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15400708</x:v>
+        <x:v>25916586</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30469,7 +30469,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11753224</x:v>
+        <x:v>33034261</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30547,7 +30547,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>352261</x:v>
+        <x:v>22522508</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30625,7 +30625,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6065501</x:v>
+        <x:v>462784</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30703,7 +30703,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10596034</x:v>
+        <x:v>29776551</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30773,7 +30773,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>676741</x:v>
+        <x:v>22344886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30843,7 +30843,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3588338</x:v>
+        <x:v>23544010</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30913,7 +30913,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4870127</x:v>
+        <x:v>7997422</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30983,7 +30983,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5833479</x:v>
+        <x:v>772366</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31053,7 +31053,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5979504</x:v>
+        <x:v>359687</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31121,7 +31121,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11126731</x:v>
+        <x:v>31625386</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31201,7 +31201,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>308348</x:v>
+        <x:v>22123134</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31281,7 +31281,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9056749</x:v>
+        <x:v>29751712</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31349,7 +31349,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10526213</x:v>
+        <x:v>6898605</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31429,7 +31429,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17877262</x:v>
+        <x:v>5023903</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31509,7 +31509,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19288607</x:v>
+        <x:v>9363769</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31589,7 +31589,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19305927</x:v>
+        <x:v>9413095</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31657,7 +31657,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31407700</x:v>
+        <x:v>14814197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31737,7 +31737,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17381560</x:v>
+        <x:v>6119481</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31817,7 +31817,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24135133</x:v>
+        <x:v>4055917</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31897,7 +31897,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31386802</x:v>
+        <x:v>14836921</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31977,7 +31977,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28792203</x:v>
+        <x:v>19599656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32057,7 +32057,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26193814</x:v>
+        <x:v>16298765</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32137,7 +32137,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31523109</x:v>
+        <x:v>14973592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32217,7 +32217,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25203241</x:v>
+        <x:v>17741319</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32297,7 +32297,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22130372</x:v>
+        <x:v>1443333</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32377,7 +32377,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29765077</x:v>
+        <x:v>12900034</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32457,7 +32457,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31601751</x:v>
+        <x:v>14408473</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32537,7 +32537,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25876280</x:v>
+        <x:v>17944293</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32617,7 +32617,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24234029</x:v>
+        <x:v>3621004</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32697,7 +32697,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22099784</x:v>
+        <x:v>1408118</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32777,7 +32777,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18339895</x:v>
+        <x:v>6721510</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32869,7 +32869,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23201172</x:v>
+        <x:v>5177679</x:v>
       </x:c>
     </x:row>
     <x:row/>
